--- a/flaskbackend/centercost_data/2024년1월.xlsx
+++ b/flaskbackend/centercost_data/2024년1월.xlsx
@@ -1,31 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KDT48\Desktop\python\DAY_9\project\PROJECT\IljiProject_v2\IljiProject_v2\flaskbackend\cost_monthly\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0773A60-88A7-47D3-8A7C-0A35D809E124}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1838" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1837" uniqueCount="271">
   <si>
     <t>코스트센터코드</t>
   </si>
@@ -838,20 +827,17 @@
   </si>
   <si>
     <t>(제)외주가공비-원자재</t>
-  </si>
-  <si>
-    <t>총비용</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -859,15 +845,8 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -913,25 +892,17 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -969,7 +940,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1003,7 +974,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1038,10 +1008,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1214,16 +1183,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E918"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="1" max="3" width="14.08203125" customWidth="1"/>
-    <col min="4" max="4" width="23.25" customWidth="1"/>
-    <col min="5" max="5" width="14.08203125" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E917"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1240,7 +1204,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1100003</v>
       </c>
@@ -1257,7 +1221,7 @@
         <v>-777102</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1100003</v>
       </c>
@@ -1274,7 +1238,7 @@
         <v>149676776</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>1100003</v>
       </c>
@@ -1291,7 +1255,7 @@
         <v>15038184</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>1100003</v>
       </c>
@@ -1308,7 +1272,7 @@
         <v>7928242</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>1100003</v>
       </c>
@@ -1322,10 +1286,10 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>1492354</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7">
         <v>1100003</v>
       </c>
@@ -1342,7 +1306,7 @@
         <v>548513</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5">
       <c r="A8">
         <v>1100003</v>
       </c>
@@ -1359,7 +1323,7 @@
         <v>21081</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5">
       <c r="A9">
         <v>1100003</v>
       </c>
@@ -1376,7 +1340,7 @@
         <v>728786</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5">
       <c r="A10">
         <v>1100003</v>
       </c>
@@ -1393,7 +1357,7 @@
         <v>11367346</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5">
       <c r="A11">
         <v>1100003</v>
       </c>
@@ -1410,7 +1374,7 @@
         <v>505860</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5">
       <c r="A12">
         <v>1100003</v>
       </c>
@@ -1427,7 +1391,7 @@
         <v>36245</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5">
       <c r="A13">
         <v>1100003</v>
       </c>
@@ -1444,7 +1408,7 @@
         <v>429149</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5">
       <c r="A14">
         <v>1100003</v>
       </c>
@@ -1461,7 +1425,7 @@
         <v>31075439</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5">
       <c r="A15">
         <v>1100003</v>
       </c>
@@ -1478,7 +1442,7 @@
         <v>2483965</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5">
       <c r="A16">
         <v>1100003</v>
       </c>
@@ -1495,7 +1459,7 @@
         <v>2386203</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5">
       <c r="A17">
         <v>1100003</v>
       </c>
@@ -1512,7 +1476,7 @@
         <v>107378</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5">
       <c r="A18">
         <v>1100003</v>
       </c>
@@ -1529,7 +1493,7 @@
         <v>8097873</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5">
       <c r="A19">
         <v>1100003</v>
       </c>
@@ -1546,7 +1510,7 @@
         <v>771121</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5">
       <c r="A20">
         <v>1100003</v>
       </c>
@@ -1563,7 +1527,7 @@
         <v>40364</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5">
       <c r="A21">
         <v>1100003</v>
       </c>
@@ -1580,7 +1544,7 @@
         <v>805980</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5">
       <c r="A22">
         <v>1100003</v>
       </c>
@@ -1597,7 +1561,7 @@
         <v>2971686</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5">
       <c r="A23">
         <v>1110001</v>
       </c>
@@ -1614,7 +1578,7 @@
         <v>5450</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5">
       <c r="A24">
         <v>1110001</v>
       </c>
@@ -1631,7 +1595,7 @@
         <v>78449</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5">
       <c r="A25">
         <v>1110002</v>
       </c>
@@ -1648,7 +1612,7 @@
         <v>4398812</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5">
       <c r="A26">
         <v>1110002</v>
       </c>
@@ -1665,7 +1629,7 @@
         <v>344087</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5">
       <c r="A27">
         <v>1110002</v>
       </c>
@@ -1682,7 +1646,7 @@
         <v>270512</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5">
       <c r="A28">
         <v>1110002</v>
       </c>
@@ -1699,7 +1663,7 @@
         <v>21696</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5">
       <c r="A29">
         <v>1110003</v>
       </c>
@@ -1716,7 +1680,7 @@
         <v>3159635</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5">
       <c r="A30">
         <v>1110003</v>
       </c>
@@ -1733,7 +1697,7 @@
         <v>16458</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5">
       <c r="A31">
         <v>1110004</v>
       </c>
@@ -1750,7 +1714,7 @@
         <v>16163709</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5">
       <c r="A32">
         <v>1110004</v>
       </c>
@@ -1767,7 +1731,7 @@
         <v>2774719</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5">
       <c r="A33">
         <v>1110004</v>
       </c>
@@ -1784,7 +1748,7 @@
         <v>1184167</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5">
       <c r="A34">
         <v>1110004</v>
       </c>
@@ -1801,7 +1765,7 @@
         <v>92070</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:5">
       <c r="A35">
         <v>1110005</v>
       </c>
@@ -1818,7 +1782,7 @@
         <v>-95735022</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5">
       <c r="A36">
         <v>1110005</v>
       </c>
@@ -1835,7 +1799,7 @@
         <v>-81251741</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5">
       <c r="A37">
         <v>1110005</v>
       </c>
@@ -1852,7 +1816,7 @@
         <v>119357020</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5">
       <c r="A38">
         <v>1110005</v>
       </c>
@@ -1869,7 +1833,7 @@
         <v>-153772459</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5">
       <c r="A39">
         <v>1110005</v>
       </c>
@@ -1886,7 +1850,7 @@
         <v>-98672</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5">
       <c r="A40">
         <v>1110005</v>
       </c>
@@ -1903,7 +1867,7 @@
         <v>-16020435</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:5">
       <c r="A41">
         <v>1110005</v>
       </c>
@@ -1920,7 +1884,7 @@
         <v>-55796499</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:5">
       <c r="A42">
         <v>1110005</v>
       </c>
@@ -1937,7 +1901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:5">
       <c r="A43">
         <v>1110005</v>
       </c>
@@ -1954,7 +1918,7 @@
         <v>-47386215</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:5">
       <c r="A44">
         <v>1110005</v>
       </c>
@@ -1971,7 +1935,7 @@
         <v>3567458</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:5">
       <c r="A45">
         <v>1110005</v>
       </c>
@@ -1988,7 +1952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:5">
       <c r="A46">
         <v>1110005</v>
       </c>
@@ -2005,7 +1969,7 @@
         <v>16420271</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:5">
       <c r="A47">
         <v>1110005</v>
       </c>
@@ -2022,7 +1986,7 @@
         <v>2244640</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:5">
       <c r="A48">
         <v>1110005</v>
       </c>
@@ -2039,7 +2003,7 @@
         <v>1659254</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:5">
       <c r="A49">
         <v>1110005</v>
       </c>
@@ -2056,7 +2020,7 @@
         <v>2103059</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5">
       <c r="A50">
         <v>1110005</v>
       </c>
@@ -2070,10 +2034,10 @@
         <v>100</v>
       </c>
       <c r="E50">
-        <v>1513756</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51">
         <v>1110005</v>
       </c>
@@ -2090,7 +2054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5">
       <c r="A52">
         <v>1110005</v>
       </c>
@@ -2107,7 +2071,7 @@
         <v>505725</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:5">
       <c r="A53">
         <v>1110005</v>
       </c>
@@ -2124,7 +2088,7 @@
         <v>93147</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5">
       <c r="A54">
         <v>1110005</v>
       </c>
@@ -2141,7 +2105,7 @@
         <v>104956</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5">
       <c r="A55">
         <v>1110005</v>
       </c>
@@ -2158,7 +2122,7 @@
         <v>28357967</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:5">
       <c r="A56">
         <v>1110005</v>
       </c>
@@ -2175,7 +2139,7 @@
         <v>1099511289</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:5">
       <c r="A57">
         <v>1110005</v>
       </c>
@@ -2192,7 +2156,7 @@
         <v>45704</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:5">
       <c r="A58">
         <v>1110005</v>
       </c>
@@ -2209,7 +2173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:5">
       <c r="A59">
         <v>1110005</v>
       </c>
@@ -2226,7 +2190,7 @@
         <v>-2593316</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:5">
       <c r="A60">
         <v>1110005</v>
       </c>
@@ -2243,7 +2207,7 @@
         <v>330144307</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:5">
       <c r="A61">
         <v>1110005</v>
       </c>
@@ -2260,7 +2224,7 @@
         <v>-234831</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:5">
       <c r="A62">
         <v>1110005</v>
       </c>
@@ -2277,7 +2241,7 @@
         <v>119843</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:5">
       <c r="A63">
         <v>1110005</v>
       </c>
@@ -2294,7 +2258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:5">
       <c r="A64">
         <v>1110005</v>
       </c>
@@ -2311,7 +2275,7 @@
         <v>408319367</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:5">
       <c r="A65">
         <v>1110005</v>
       </c>
@@ -2328,7 +2292,7 @@
         <v>137574279</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:5">
       <c r="A66">
         <v>1110005</v>
       </c>
@@ -2345,7 +2309,7 @@
         <v>41246634</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:5">
       <c r="A67">
         <v>1110005</v>
       </c>
@@ -2362,7 +2326,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:5">
       <c r="A68">
         <v>1110005</v>
       </c>
@@ -2379,7 +2343,7 @@
         <v>-74477</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:5">
       <c r="A69">
         <v>1110005</v>
       </c>
@@ -2396,7 +2360,7 @@
         <v>52072185</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:5">
       <c r="A70">
         <v>1110005</v>
       </c>
@@ -2413,7 +2377,7 @@
         <v>765111</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:5">
       <c r="A71">
         <v>1110005</v>
       </c>
@@ -2430,7 +2394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:5">
       <c r="A72">
         <v>1110005</v>
       </c>
@@ -2447,7 +2411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:5">
       <c r="A73">
         <v>1110005</v>
       </c>
@@ -2464,7 +2428,7 @@
         <v>1859277</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:5">
       <c r="A74">
         <v>1110005</v>
       </c>
@@ -2478,10 +2442,10 @@
         <v>145</v>
       </c>
       <c r="E74">
-        <v>1072864972</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75">
         <v>1110005</v>
       </c>
@@ -2498,7 +2462,7 @@
         <v>-328</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:5">
       <c r="A76">
         <v>1110005</v>
       </c>
@@ -2515,7 +2479,7 @@
         <v>5824512</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:5">
       <c r="A77">
         <v>1110005</v>
       </c>
@@ -2532,7 +2496,7 @@
         <v>2230869</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:5">
       <c r="A78">
         <v>1110005</v>
       </c>
@@ -2549,7 +2513,7 @@
         <v>-6566511</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:5">
       <c r="A79">
         <v>1110006</v>
       </c>
@@ -2566,7 +2530,7 @@
         <v>-3125650</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:5">
       <c r="A80">
         <v>1110006</v>
       </c>
@@ -2583,7 +2547,7 @@
         <v>16290547</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:5">
       <c r="A81">
         <v>1110006</v>
       </c>
@@ -2600,7 +2564,7 @@
         <v>2247068</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:5">
       <c r="A82">
         <v>1110006</v>
       </c>
@@ -2617,7 +2581,7 @@
         <v>2054183</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:5">
       <c r="A83">
         <v>1110006</v>
       </c>
@@ -2634,7 +2598,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:5">
       <c r="A84">
         <v>1110006</v>
       </c>
@@ -2651,7 +2615,7 @@
         <v>121417</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:5">
       <c r="A85">
         <v>1110006</v>
       </c>
@@ -2665,10 +2629,10 @@
         <v>100</v>
       </c>
       <c r="E85">
-        <v>50866</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86">
         <v>1110006</v>
       </c>
@@ -2685,7 +2649,7 @@
         <v>388596</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:5">
       <c r="A87">
         <v>1110006</v>
       </c>
@@ -2702,7 +2666,7 @@
         <v>-29489</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:5">
       <c r="A88">
         <v>1110006</v>
       </c>
@@ -2719,7 +2683,7 @@
         <v>89851</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:5">
       <c r="A89">
         <v>1110006</v>
       </c>
@@ -2736,7 +2700,7 @@
         <v>13819939</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:5">
       <c r="A90">
         <v>1110006</v>
       </c>
@@ -2753,7 +2717,7 @@
         <v>14004624</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:5">
       <c r="A91">
         <v>1110006</v>
       </c>
@@ -2770,7 +2734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:5">
       <c r="A92">
         <v>1110006</v>
       </c>
@@ -2787,7 +2751,7 @@
         <v>8951744</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:5">
       <c r="A93">
         <v>1110006</v>
       </c>
@@ -2804,7 +2768,7 @@
         <v>268595</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:5">
       <c r="A94">
         <v>1110006</v>
       </c>
@@ -2821,7 +2785,7 @@
         <v>91276</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:5">
       <c r="A95">
         <v>1110006</v>
       </c>
@@ -2838,7 +2802,7 @@
         <v>146739</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:5">
       <c r="A96">
         <v>1110006</v>
       </c>
@@ -2855,7 +2819,7 @@
         <v>272831</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:5">
       <c r="A97">
         <v>1110006</v>
       </c>
@@ -2872,7 +2836,7 @@
         <v>652261</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:5">
       <c r="A98">
         <v>1110006</v>
       </c>
@@ -2889,7 +2853,7 @@
         <v>1803157</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:5">
       <c r="A99">
         <v>1110006</v>
       </c>
@@ -2906,7 +2870,7 @@
         <v>706109</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:5">
       <c r="A100">
         <v>1110007</v>
       </c>
@@ -2923,7 +2887,7 @@
         <v>-269764</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:5">
       <c r="A101">
         <v>1110007</v>
       </c>
@@ -2940,7 +2904,7 @@
         <v>35894327</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:5">
       <c r="A102">
         <v>1110007</v>
       </c>
@@ -2957,7 +2921,7 @@
         <v>4296611</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:5">
       <c r="A103">
         <v>1110007</v>
       </c>
@@ -2974,7 +2938,7 @@
         <v>4367154</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:5">
       <c r="A104">
         <v>1110007</v>
       </c>
@@ -2991,7 +2955,7 @@
         <v>3874034</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:5">
       <c r="A105">
         <v>1110007</v>
       </c>
@@ -3008,7 +2972,7 @@
         <v>2344285</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:5">
       <c r="A106">
         <v>1110007</v>
       </c>
@@ -3025,7 +2989,7 @@
         <v>274590</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:5">
       <c r="A107">
         <v>1110007</v>
       </c>
@@ -3042,7 +3006,7 @@
         <v>1732057</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:5">
       <c r="A108">
         <v>1110007</v>
       </c>
@@ -3059,7 +3023,7 @@
         <v>1087000</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:5">
       <c r="A109">
         <v>1110007</v>
       </c>
@@ -3076,7 +3040,7 @@
         <v>17045242</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:5">
       <c r="A110">
         <v>1110007</v>
       </c>
@@ -3093,7 +3057,7 @@
         <v>177014</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:5">
       <c r="A111">
         <v>1110007</v>
       </c>
@@ -3110,7 +3074,7 @@
         <v>1970495</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:5">
       <c r="A112">
         <v>1110007</v>
       </c>
@@ -3127,7 +3091,7 @@
         <v>1384715</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:5">
       <c r="A113">
         <v>1110007</v>
       </c>
@@ -3144,7 +3108,7 @@
         <v>5492</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:5">
       <c r="A114">
         <v>1110007</v>
       </c>
@@ -3161,7 +3125,7 @@
         <v>424570</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:5">
       <c r="A115">
         <v>1110007</v>
       </c>
@@ -3178,7 +3142,7 @@
         <v>3246558</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:5">
       <c r="A116">
         <v>1110007</v>
       </c>
@@ -3195,7 +3159,7 @@
         <v>495791</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:5">
       <c r="A117">
         <v>1110007</v>
       </c>
@@ -3212,7 +3176,7 @@
         <v>2943</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:5">
       <c r="A118">
         <v>1110007</v>
       </c>
@@ -3229,7 +3193,7 @@
         <v>67140</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:5">
       <c r="A119">
         <v>1110007</v>
       </c>
@@ -3246,7 +3210,7 @@
         <v>34698</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:5">
       <c r="A120">
         <v>1110007</v>
       </c>
@@ -3263,7 +3227,7 @@
         <v>679287</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:5">
       <c r="A121">
         <v>1110007</v>
       </c>
@@ -3280,7 +3244,7 @@
         <v>491125</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:5">
       <c r="A122">
         <v>1110007</v>
       </c>
@@ -3297,7 +3261,7 @@
         <v>137824</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:5">
       <c r="A123">
         <v>1110007</v>
       </c>
@@ -3314,7 +3278,7 @@
         <v>103860606</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:5">
       <c r="A124">
         <v>1110007</v>
       </c>
@@ -3331,7 +3295,7 @@
         <v>373676</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:5">
       <c r="A125">
         <v>1110007</v>
       </c>
@@ -3348,7 +3312,7 @@
         <v>421191</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:5">
       <c r="A126">
         <v>1110007</v>
       </c>
@@ -3365,7 +3329,7 @@
         <v>1008640</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:5">
       <c r="A127">
         <v>1110007</v>
       </c>
@@ -3382,7 +3346,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:5">
       <c r="A128">
         <v>1110007</v>
       </c>
@@ -3399,7 +3363,7 @@
         <v>629228</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:5">
       <c r="A129">
         <v>1110007</v>
       </c>
@@ -3416,7 +3380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:5">
       <c r="A130">
         <v>1110007</v>
       </c>
@@ -3433,7 +3397,7 @@
         <v>27283</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:5">
       <c r="A131">
         <v>1110007</v>
       </c>
@@ -3450,7 +3414,7 @@
         <v>3300499</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:5">
       <c r="A132">
         <v>1110007</v>
       </c>
@@ -3467,7 +3431,7 @@
         <v>1617660</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:5">
       <c r="A133">
         <v>1110007</v>
       </c>
@@ -3484,7 +3448,7 @@
         <v>9608</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:5">
       <c r="A134">
         <v>1110007</v>
       </c>
@@ -3501,7 +3465,7 @@
         <v>20789870</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:5">
       <c r="A135">
         <v>1110007</v>
       </c>
@@ -3518,7 +3482,7 @@
         <v>28016612</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:5">
       <c r="A136">
         <v>1110007</v>
       </c>
@@ -3535,7 +3499,7 @@
         <v>22571930</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:5">
       <c r="A137">
         <v>1110007</v>
       </c>
@@ -3552,7 +3516,7 @@
         <v>15179788</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:5">
       <c r="A138">
         <v>1110007</v>
       </c>
@@ -3569,7 +3533,7 @@
         <v>12700810</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:5">
       <c r="A139">
         <v>1110007</v>
       </c>
@@ -3586,7 +3550,7 @@
         <v>14313729</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:5">
       <c r="A140">
         <v>1110007</v>
       </c>
@@ -3603,7 +3567,7 @@
         <v>4599061</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:5">
       <c r="A141">
         <v>1110007</v>
       </c>
@@ -3620,7 +3584,7 @@
         <v>3454234</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:5">
       <c r="A142">
         <v>1110007</v>
       </c>
@@ -3637,7 +3601,7 @@
         <v>5587</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:5">
       <c r="A143">
         <v>1110007</v>
       </c>
@@ -3654,7 +3618,7 @@
         <v>4262140</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:5">
       <c r="A144">
         <v>1110007</v>
       </c>
@@ -3671,7 +3635,7 @@
         <v>110231</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:5">
       <c r="A145">
         <v>1110007</v>
       </c>
@@ -3688,7 +3652,7 @@
         <v>867643</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:5">
       <c r="A146">
         <v>1110007</v>
       </c>
@@ -3705,7 +3669,7 @@
         <v>114994</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:5">
       <c r="A147">
         <v>1110007</v>
       </c>
@@ -3722,7 +3686,7 @@
         <v>1139727</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:5">
       <c r="A148">
         <v>1110007</v>
       </c>
@@ -3739,7 +3703,7 @@
         <v>9702280</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:5">
       <c r="A149">
         <v>1110007</v>
       </c>
@@ -3756,7 +3720,7 @@
         <v>396073</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:5">
       <c r="A150">
         <v>1110007</v>
       </c>
@@ -3773,7 +3737,7 @@
         <v>20287</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:5">
       <c r="A151">
         <v>1110007</v>
       </c>
@@ -3790,7 +3754,7 @@
         <v>4320088</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:5">
       <c r="A152">
         <v>1110007</v>
       </c>
@@ -3807,7 +3771,7 @@
         <v>138696</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:5">
       <c r="A153">
         <v>1110020</v>
       </c>
@@ -3824,7 +3788,7 @@
         <v>26561</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:5">
       <c r="A154">
         <v>1110020</v>
       </c>
@@ -3841,7 +3805,7 @@
         <v>771931</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:5">
       <c r="A155">
         <v>1110020</v>
       </c>
@@ -3858,7 +3822,7 @@
         <v>29279</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:5">
       <c r="A156">
         <v>1110021</v>
       </c>
@@ -3875,7 +3839,7 @@
         <v>200066</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:5">
       <c r="A157">
         <v>1110021</v>
       </c>
@@ -3892,7 +3856,7 @@
         <v>5088</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:5">
       <c r="A158">
         <v>1110021</v>
       </c>
@@ -3909,7 +3873,7 @@
         <v>153953</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:5">
       <c r="A159">
         <v>1110021</v>
       </c>
@@ -3926,7 +3890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:5">
       <c r="A160">
         <v>1110021</v>
       </c>
@@ -3943,7 +3907,7 @@
         <v>15305</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:5">
       <c r="A161">
         <v>1110021</v>
       </c>
@@ -3960,7 +3924,7 @@
         <v>48439196</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:5">
       <c r="A162">
         <v>1110021</v>
       </c>
@@ -3977,7 +3941,7 @@
         <v>4296718</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:5">
       <c r="A163">
         <v>1110021</v>
       </c>
@@ -3994,7 +3958,7 @@
         <v>10830</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:5">
       <c r="A164">
         <v>1110021</v>
       </c>
@@ -4011,7 +3975,7 @@
         <v>216295</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:5">
       <c r="A165">
         <v>1110021</v>
       </c>
@@ -4028,7 +3992,7 @@
         <v>104258</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:5">
       <c r="A166">
         <v>1110021</v>
       </c>
@@ -4045,7 +4009,7 @@
         <v>23476713</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:5">
       <c r="A167">
         <v>1110021</v>
       </c>
@@ -4062,7 +4026,7 @@
         <v>2772331</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:5">
       <c r="A168">
         <v>1110021</v>
       </c>
@@ -4079,7 +4043,7 @@
         <v>120473</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:5">
       <c r="A169">
         <v>1110021</v>
       </c>
@@ -4096,7 +4060,7 @@
         <v>2650869</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:5">
       <c r="A170">
         <v>1110021</v>
       </c>
@@ -4113,7 +4077,7 @@
         <v>149421</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:5">
       <c r="A171">
         <v>1110022</v>
       </c>
@@ -4130,7 +4094,7 @@
         <v>685220</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:5">
       <c r="A172">
         <v>1110022</v>
       </c>
@@ -4147,7 +4111,7 @@
         <v>6292</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:5">
       <c r="A173">
         <v>1110022</v>
       </c>
@@ -4164,7 +4128,7 @@
         <v>154679</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:5">
       <c r="A174">
         <v>1110022</v>
       </c>
@@ -4178,10 +4142,10 @@
         <v>189</v>
       </c>
       <c r="E174">
-        <v>779182</v>
-      </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
       <c r="A175">
         <v>1110022</v>
       </c>
@@ -4198,7 +4162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:5">
       <c r="A176">
         <v>1110022</v>
       </c>
@@ -4215,7 +4179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:5">
       <c r="A177">
         <v>1110022</v>
       </c>
@@ -4232,7 +4196,7 @@
         <v>337170</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:5">
       <c r="A178">
         <v>1110022</v>
       </c>
@@ -4249,7 +4213,7 @@
         <v>22595910</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:5">
       <c r="A179">
         <v>1110022</v>
       </c>
@@ -4266,7 +4230,7 @@
         <v>2459492</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:5">
       <c r="A180">
         <v>1110022</v>
       </c>
@@ -4283,7 +4247,7 @@
         <v>111726</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:5">
       <c r="A181">
         <v>1110022</v>
       </c>
@@ -4300,7 +4264,7 @@
         <v>2541608</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:5">
       <c r="A182">
         <v>1110022</v>
       </c>
@@ -4317,7 +4281,7 @@
         <v>32816</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:5">
       <c r="A183">
         <v>1110023</v>
       </c>
@@ -4334,7 +4298,7 @@
         <v>26337</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:5">
       <c r="A184">
         <v>1110023</v>
       </c>
@@ -4351,7 +4315,7 @@
         <v>2352500</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:5">
       <c r="A185">
         <v>1110023</v>
       </c>
@@ -4368,7 +4332,7 @@
         <v>255043</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:5">
       <c r="A186">
         <v>1110023</v>
       </c>
@@ -4385,7 +4349,7 @@
         <v>11280</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:5">
       <c r="A187">
         <v>1110023</v>
       </c>
@@ -4402,7 +4366,7 @@
         <v>246612</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:5">
       <c r="A188">
         <v>1110024</v>
       </c>
@@ -4419,7 +4383,7 @@
         <v>-389910</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:5">
       <c r="A189">
         <v>1110024</v>
       </c>
@@ -4436,7 +4400,7 @@
         <v>110409</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:5">
       <c r="A190">
         <v>1110024</v>
       </c>
@@ -4453,7 +4417,7 @@
         <v>165198</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:5">
       <c r="A191">
         <v>1110024</v>
       </c>
@@ -4467,10 +4431,10 @@
         <v>189</v>
       </c>
       <c r="E191">
-        <v>444403</v>
-      </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
       <c r="A192">
         <v>1110024</v>
       </c>
@@ -4487,7 +4451,7 @@
         <v>6242129</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:5">
       <c r="A193">
         <v>1110024</v>
       </c>
@@ -4504,7 +4468,7 @@
         <v>179590</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:5">
       <c r="A194">
         <v>1110024</v>
       </c>
@@ -4521,7 +4485,7 @@
         <v>18696941</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:5">
       <c r="A195">
         <v>1110024</v>
       </c>
@@ -4538,7 +4502,7 @@
         <v>2293028</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:5">
       <c r="A196">
         <v>1110024</v>
       </c>
@@ -4555,7 +4519,7 @@
         <v>96002</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:5">
       <c r="A197">
         <v>1110024</v>
       </c>
@@ -4572,7 +4536,7 @@
         <v>2204539</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:5">
       <c r="A198">
         <v>1110024</v>
       </c>
@@ -4589,7 +4553,7 @@
         <v>81765</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:5">
       <c r="A199">
         <v>1110026</v>
       </c>
@@ -4606,7 +4570,7 @@
         <v>71721</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:5">
       <c r="A200">
         <v>1110026</v>
       </c>
@@ -4623,7 +4587,7 @@
         <v>237562</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:5">
       <c r="A201">
         <v>1110026</v>
       </c>
@@ -4637,10 +4601,10 @@
         <v>189</v>
       </c>
       <c r="E201">
-        <v>3139945</v>
-      </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
       <c r="A202">
         <v>1110026</v>
       </c>
@@ -4657,7 +4621,7 @@
         <v>14302835</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:5">
       <c r="A203">
         <v>1110026</v>
       </c>
@@ -4674,7 +4638,7 @@
         <v>515679</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:5">
       <c r="A204">
         <v>1110026</v>
       </c>
@@ -4691,7 +4655,7 @@
         <v>40031947</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:5">
       <c r="A205">
         <v>1110026</v>
       </c>
@@ -4708,7 +4672,7 @@
         <v>4361017</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:5">
       <c r="A206">
         <v>1110026</v>
       </c>
@@ -4725,7 +4689,7 @@
         <v>218289</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:5">
       <c r="A207">
         <v>1110026</v>
       </c>
@@ -4742,7 +4706,7 @@
         <v>4885731</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:5">
       <c r="A208">
         <v>1110026</v>
       </c>
@@ -4759,7 +4723,7 @@
         <v>46486</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:5">
       <c r="A209">
         <v>1110026</v>
       </c>
@@ -4776,7 +4740,7 @@
         <v>87547</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:5">
       <c r="A210">
         <v>1110030</v>
       </c>
@@ -4793,7 +4757,7 @@
         <v>15252</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:5">
       <c r="A211">
         <v>1110031</v>
       </c>
@@ -4810,7 +4774,7 @@
         <v>133425</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:5">
       <c r="A212">
         <v>1110031</v>
       </c>
@@ -4827,7 +4791,7 @@
         <v>3715871</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:5">
       <c r="A213">
         <v>1110031</v>
       </c>
@@ -4844,7 +4808,7 @@
         <v>18177540</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:5">
       <c r="A214">
         <v>1110031</v>
       </c>
@@ -4861,7 +4825,7 @@
         <v>1915693</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:5">
       <c r="A215">
         <v>1110031</v>
       </c>
@@ -4878,7 +4842,7 @@
         <v>116785355</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:5">
       <c r="A216">
         <v>1110031</v>
       </c>
@@ -4895,7 +4859,7 @@
         <v>18033</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:5">
       <c r="A217">
         <v>1110031</v>
       </c>
@@ -4912,7 +4876,7 @@
         <v>102375</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:5">
       <c r="A218">
         <v>1110031</v>
       </c>
@@ -4926,10 +4890,10 @@
         <v>189</v>
       </c>
       <c r="E218">
-        <v>605164</v>
-      </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
       <c r="A219">
         <v>1110031</v>
       </c>
@@ -4946,7 +4910,7 @@
         <v>2167770</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:5">
       <c r="A220">
         <v>1110031</v>
       </c>
@@ -4963,7 +4927,7 @@
         <v>180800</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:5">
       <c r="A221">
         <v>1110031</v>
       </c>
@@ -4980,7 +4944,7 @@
         <v>202800</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:5">
       <c r="A222">
         <v>1110031</v>
       </c>
@@ -4997,7 +4961,7 @@
         <v>12196007</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:5">
       <c r="A223">
         <v>1110031</v>
       </c>
@@ -5014,7 +4978,7 @@
         <v>3076835</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:5">
       <c r="A224">
         <v>1110031</v>
       </c>
@@ -5031,7 +4995,7 @@
         <v>94212</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:5">
       <c r="A225">
         <v>1110031</v>
       </c>
@@ -5048,7 +5012,7 @@
         <v>220817</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:5">
       <c r="A226">
         <v>1110031</v>
       </c>
@@ -5065,7 +5029,7 @@
         <v>1820722</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:5">
       <c r="A227">
         <v>1110031</v>
       </c>
@@ -5082,7 +5046,7 @@
         <v>2400961</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:5">
       <c r="A228">
         <v>1110031</v>
       </c>
@@ -5099,7 +5063,7 @@
         <v>691114</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:5">
       <c r="A229">
         <v>1110031</v>
       </c>
@@ -5116,7 +5080,7 @@
         <v>6372036</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:5">
       <c r="A230">
         <v>1110031</v>
       </c>
@@ -5133,7 +5097,7 @@
         <v>922015</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:5">
       <c r="A231">
         <v>1110031</v>
       </c>
@@ -5150,7 +5114,7 @@
         <v>105926</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:5">
       <c r="A232">
         <v>1110031</v>
       </c>
@@ -5167,7 +5131,7 @@
         <v>8504202</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:5">
       <c r="A233">
         <v>1110031</v>
       </c>
@@ -5184,7 +5148,7 @@
         <v>2413421</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:5">
       <c r="A234">
         <v>1110031</v>
       </c>
@@ -5201,7 +5165,7 @@
         <v>22888</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:5">
       <c r="A235">
         <v>1110031</v>
       </c>
@@ -5218,7 +5182,7 @@
         <v>32995</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:5">
       <c r="A236">
         <v>1110031</v>
       </c>
@@ -5235,7 +5199,7 @@
         <v>471962</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:5">
       <c r="A237">
         <v>1110031</v>
       </c>
@@ -5252,7 +5216,7 @@
         <v>86753</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:5">
       <c r="A238">
         <v>1110031</v>
       </c>
@@ -5269,7 +5233,7 @@
         <v>130018</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:5">
       <c r="A239">
         <v>1110031</v>
       </c>
@@ -5286,7 +5250,7 @@
         <v>1342473</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:5">
       <c r="A240">
         <v>1110031</v>
       </c>
@@ -5303,7 +5267,7 @@
         <v>3566943</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:5">
       <c r="A241">
         <v>1110031</v>
       </c>
@@ -5320,7 +5284,7 @@
         <v>7484864</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:5">
       <c r="A242">
         <v>1110031</v>
       </c>
@@ -5337,7 +5301,7 @@
         <v>4776221</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:5">
       <c r="A243">
         <v>1110031</v>
       </c>
@@ -5354,7 +5318,7 @@
         <v>17114</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:5">
       <c r="A244">
         <v>1110032</v>
       </c>
@@ -5371,7 +5335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:5">
       <c r="A245">
         <v>1110032</v>
       </c>
@@ -5388,7 +5352,7 @@
         <v>79191</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:5">
       <c r="A246">
         <v>1110032</v>
       </c>
@@ -5405,7 +5369,7 @@
         <v>88085</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:5">
       <c r="A247">
         <v>1110032</v>
       </c>
@@ -5422,7 +5386,7 @@
         <v>244322</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:5">
       <c r="A248">
         <v>1110032</v>
       </c>
@@ -5439,7 +5403,7 @@
         <v>22804050</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:5">
       <c r="A249">
         <v>1110032</v>
       </c>
@@ -5456,7 +5420,7 @@
         <v>2052142</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:5">
       <c r="A250">
         <v>1110032</v>
       </c>
@@ -5473,7 +5437,7 @@
         <v>45486</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:5">
       <c r="A251">
         <v>1110032</v>
       </c>
@@ -5490,7 +5454,7 @@
         <v>226314</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:5">
       <c r="A252">
         <v>1110032</v>
       </c>
@@ -5504,10 +5468,10 @@
         <v>189</v>
       </c>
       <c r="E252">
-        <v>692485</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
       <c r="A253">
         <v>1110032</v>
       </c>
@@ -5524,7 +5488,7 @@
         <v>2602477</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:5">
       <c r="A254">
         <v>1110032</v>
       </c>
@@ -5541,7 +5505,7 @@
         <v>529930</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:5">
       <c r="A255">
         <v>1110032</v>
       </c>
@@ -5558,7 +5522,7 @@
         <v>30092</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:5">
       <c r="A256">
         <v>1110032</v>
       </c>
@@ -5575,7 +5539,7 @@
         <v>649633</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:5">
       <c r="A257">
         <v>1110032</v>
       </c>
@@ -5592,7 +5556,7 @@
         <v>113015</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:5">
       <c r="A258">
         <v>1110032</v>
       </c>
@@ -5609,7 +5573,7 @@
         <v>72828</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:5">
       <c r="A259">
         <v>1110032</v>
       </c>
@@ -5626,7 +5590,7 @@
         <v>119069</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:5">
       <c r="A260">
         <v>1110032</v>
       </c>
@@ -5643,7 +5607,7 @@
         <v>48121</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:5">
       <c r="A261">
         <v>1110032</v>
       </c>
@@ -5660,7 +5624,7 @@
         <v>8329</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:5">
       <c r="A262">
         <v>1110032</v>
       </c>
@@ -5677,7 +5641,7 @@
         <v>19092</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:5">
       <c r="A263">
         <v>1110032</v>
       </c>
@@ -5694,7 +5658,7 @@
         <v>444714</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:5">
       <c r="A264">
         <v>1110032</v>
       </c>
@@ -5711,7 +5675,7 @@
         <v>553059</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:5">
       <c r="A265">
         <v>1110032</v>
       </c>
@@ -5728,7 +5692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:5">
       <c r="A266">
         <v>1110032</v>
       </c>
@@ -5745,7 +5709,7 @@
         <v>47634</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:5">
       <c r="A267">
         <v>1110032</v>
       </c>
@@ -5762,7 +5726,7 @@
         <v>423262</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:5">
       <c r="A268">
         <v>1110032</v>
       </c>
@@ -5779,7 +5743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:5">
       <c r="A269">
         <v>1110032</v>
       </c>
@@ -5796,7 +5760,7 @@
         <v>51584</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:5">
       <c r="A270">
         <v>1110032</v>
       </c>
@@ -5813,7 +5777,7 @@
         <v>96596</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:5">
       <c r="A271">
         <v>1110032</v>
       </c>
@@ -5830,7 +5794,7 @@
         <v>1339410</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:5">
       <c r="A272">
         <v>1110032</v>
       </c>
@@ -5847,7 +5811,7 @@
         <v>2166830</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:5">
       <c r="A273">
         <v>1110032</v>
       </c>
@@ -5864,7 +5828,7 @@
         <v>5698</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:5">
       <c r="A274">
         <v>1110032</v>
       </c>
@@ -5881,7 +5845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:5">
       <c r="A275">
         <v>1110032</v>
       </c>
@@ -5898,7 +5862,7 @@
         <v>24162</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:5">
       <c r="A276">
         <v>1110032</v>
       </c>
@@ -5915,7 +5879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:5">
       <c r="A277">
         <v>1110032</v>
       </c>
@@ -5932,7 +5896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:5">
       <c r="A278">
         <v>1110034</v>
       </c>
@@ -5949,7 +5913,7 @@
         <v>-7311073</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:5">
       <c r="A279">
         <v>1110034</v>
       </c>
@@ -5966,7 +5930,7 @@
         <v>2963804</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:5">
       <c r="A280">
         <v>1110034</v>
       </c>
@@ -5983,7 +5947,7 @@
         <v>28516</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:5">
       <c r="A281">
         <v>1110034</v>
       </c>
@@ -6000,7 +5964,7 @@
         <v>41208168</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:5">
       <c r="A282">
         <v>1110034</v>
       </c>
@@ -6017,7 +5981,7 @@
         <v>18161730</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:5">
       <c r="A283">
         <v>1110034</v>
       </c>
@@ -6034,7 +5998,7 @@
         <v>1451655</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:5">
       <c r="A284">
         <v>1110034</v>
       </c>
@@ -6051,7 +6015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:5">
       <c r="A285">
         <v>1110034</v>
       </c>
@@ -6068,7 +6032,7 @@
         <v>259189</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:5">
       <c r="A286">
         <v>1110034</v>
       </c>
@@ -6082,10 +6046,10 @@
         <v>189</v>
       </c>
       <c r="E286">
-        <v>636384</v>
-      </c>
-    </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5">
       <c r="A287">
         <v>1110034</v>
       </c>
@@ -6102,7 +6066,7 @@
         <v>1871528</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:5">
       <c r="A288">
         <v>1110034</v>
       </c>
@@ -6119,7 +6083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:5">
       <c r="A289">
         <v>1110034</v>
       </c>
@@ -6136,7 +6100,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:5">
       <c r="A290">
         <v>1110034</v>
       </c>
@@ -6153,7 +6117,7 @@
         <v>85356</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:5">
       <c r="A291">
         <v>1110034</v>
       </c>
@@ -6170,7 +6134,7 @@
         <v>1552267</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:5">
       <c r="A292">
         <v>1110034</v>
       </c>
@@ -6187,7 +6151,7 @@
         <v>6145445</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:5">
       <c r="A293">
         <v>1110034</v>
       </c>
@@ -6204,7 +6168,7 @@
         <v>74618</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:5">
       <c r="A294">
         <v>1110035</v>
       </c>
@@ -6221,7 +6185,7 @@
         <v>163102</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:5">
       <c r="A295">
         <v>1110035</v>
       </c>
@@ -6238,7 +6202,7 @@
         <v>88545899</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:5">
       <c r="A296">
         <v>1110035</v>
       </c>
@@ -6252,10 +6216,10 @@
         <v>219</v>
       </c>
       <c r="E296">
-        <v>54241027</v>
-      </c>
-    </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5">
       <c r="A297">
         <v>1110035</v>
       </c>
@@ -6272,7 +6236,7 @@
         <v>4072368</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:5">
       <c r="A298">
         <v>1110035</v>
       </c>
@@ -6289,7 +6253,7 @@
         <v>763287</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:5">
       <c r="A299">
         <v>1110035</v>
       </c>
@@ -6303,10 +6267,10 @@
         <v>189</v>
       </c>
       <c r="E299">
-        <v>3719252</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5">
       <c r="A300">
         <v>1110035</v>
       </c>
@@ -6323,7 +6287,7 @@
         <v>5921814</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:5">
       <c r="A301">
         <v>1110035</v>
       </c>
@@ -6340,7 +6304,7 @@
         <v>359162</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:5">
       <c r="A302">
         <v>1110036</v>
       </c>
@@ -6357,7 +6321,7 @@
         <v>14905</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:5">
       <c r="A303">
         <v>1110036</v>
       </c>
@@ -6374,7 +6338,7 @@
         <v>41618991</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:5">
       <c r="A304">
         <v>1110036</v>
       </c>
@@ -6388,10 +6352,10 @@
         <v>219</v>
       </c>
       <c r="E304">
-        <v>26907544</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5">
       <c r="A305">
         <v>1110036</v>
       </c>
@@ -6408,7 +6372,7 @@
         <v>3338828</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:5">
       <c r="A306">
         <v>1110036</v>
       </c>
@@ -6425,7 +6389,7 @@
         <v>550381</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:5">
       <c r="A307">
         <v>1110036</v>
       </c>
@@ -6439,10 +6403,10 @@
         <v>189</v>
       </c>
       <c r="E307">
-        <v>1924306</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5">
       <c r="A308">
         <v>1110036</v>
       </c>
@@ -6459,7 +6423,7 @@
         <v>4653913</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:5">
       <c r="A309">
         <v>1110036</v>
       </c>
@@ -6476,7 +6440,7 @@
         <v>3023075</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:5">
       <c r="A310">
         <v>1110036</v>
       </c>
@@ -6493,7 +6457,7 @@
         <v>185825</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:5">
       <c r="A311">
         <v>1110037</v>
       </c>
@@ -6510,7 +6474,7 @@
         <v>67714</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:5">
       <c r="A312">
         <v>1110037</v>
       </c>
@@ -6527,7 +6491,7 @@
         <v>191936384</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:5">
       <c r="A313">
         <v>1110037</v>
       </c>
@@ -6541,10 +6505,10 @@
         <v>219</v>
       </c>
       <c r="E313">
-        <v>51920710</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5">
       <c r="A314">
         <v>1110037</v>
       </c>
@@ -6561,7 +6525,7 @@
         <v>4539993</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:5">
       <c r="A315">
         <v>1110037</v>
       </c>
@@ -6575,10 +6539,10 @@
         <v>189</v>
       </c>
       <c r="E315">
-        <v>2505072</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5">
       <c r="A316">
         <v>1110037</v>
       </c>
@@ -6595,7 +6559,7 @@
         <v>10421389</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:5">
       <c r="A317">
         <v>1110037</v>
       </c>
@@ -6612,7 +6576,7 @@
         <v>492650</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:5">
       <c r="A318">
         <v>1110037</v>
       </c>
@@ -6629,7 +6593,7 @@
         <v>69444788</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:5">
       <c r="A319">
         <v>1110037</v>
       </c>
@@ -6646,7 +6610,7 @@
         <v>352438</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:5">
       <c r="A320">
         <v>1110038</v>
       </c>
@@ -6663,7 +6627,7 @@
         <v>15691</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:5">
       <c r="A321">
         <v>1110038</v>
       </c>
@@ -6680,7 +6644,7 @@
         <v>39175759</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:5">
       <c r="A322">
         <v>1110038</v>
       </c>
@@ -6694,10 +6658,10 @@
         <v>219</v>
       </c>
       <c r="E322">
-        <v>17246002</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5">
       <c r="A323">
         <v>1110038</v>
       </c>
@@ -6714,7 +6678,7 @@
         <v>3517397</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:5">
       <c r="A324">
         <v>1110038</v>
       </c>
@@ -6731,7 +6695,7 @@
         <v>348791</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:5">
       <c r="A325">
         <v>1110038</v>
       </c>
@@ -6745,10 +6709,10 @@
         <v>189</v>
       </c>
       <c r="E325">
-        <v>3273377</v>
-      </c>
-    </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5">
       <c r="A326">
         <v>1110038</v>
       </c>
@@ -6765,7 +6729,7 @@
         <v>3996273</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:5">
       <c r="A327">
         <v>1110038</v>
       </c>
@@ -6782,7 +6746,7 @@
         <v>158464</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:5">
       <c r="A328">
         <v>1110039</v>
       </c>
@@ -6799,7 +6763,7 @@
         <v>49066</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:5">
       <c r="A329">
         <v>1110039</v>
       </c>
@@ -6816,7 +6780,7 @@
         <v>26053039</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:5">
       <c r="A330">
         <v>1110039</v>
       </c>
@@ -6830,10 +6794,10 @@
         <v>219</v>
       </c>
       <c r="E330">
-        <v>7809768</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5">
       <c r="A331">
         <v>1110039</v>
       </c>
@@ -6850,7 +6814,7 @@
         <v>1294120</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:5">
       <c r="A332">
         <v>1110039</v>
       </c>
@@ -6864,10 +6828,10 @@
         <v>189</v>
       </c>
       <c r="E332">
-        <v>100702</v>
-      </c>
-    </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5">
       <c r="A333">
         <v>1110039</v>
       </c>
@@ -6884,7 +6848,7 @@
         <v>1819092</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:5">
       <c r="A334">
         <v>1110039</v>
       </c>
@@ -6901,7 +6865,7 @@
         <v>132190</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:5">
       <c r="A335">
         <v>1110039</v>
       </c>
@@ -6918,7 +6882,7 @@
         <v>659958</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:5">
       <c r="A336">
         <v>1110039</v>
       </c>
@@ -6935,7 +6899,7 @@
         <v>117218</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:5">
       <c r="A337">
         <v>1110040</v>
       </c>
@@ -6952,7 +6916,7 @@
         <v>62037</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:5">
       <c r="A338">
         <v>1110040</v>
       </c>
@@ -6969,7 +6933,7 @@
         <v>9252653</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:5">
       <c r="A339">
         <v>1110040</v>
       </c>
@@ -6983,10 +6947,10 @@
         <v>219</v>
       </c>
       <c r="E339">
-        <v>12104036</v>
-      </c>
-    </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5">
       <c r="A340">
         <v>1110040</v>
       </c>
@@ -7003,7 +6967,7 @@
         <v>1006842</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:5">
       <c r="A341">
         <v>1110040</v>
       </c>
@@ -7020,7 +6984,7 @@
         <v>61917</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:5">
       <c r="A342">
         <v>1110040</v>
       </c>
@@ -7034,10 +6998,10 @@
         <v>189</v>
       </c>
       <c r="E342">
-        <v>477396</v>
-      </c>
-    </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5">
       <c r="A343">
         <v>1110040</v>
       </c>
@@ -7054,7 +7018,7 @@
         <v>1197318</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:5">
       <c r="A344">
         <v>1110040</v>
       </c>
@@ -7071,7 +7035,7 @@
         <v>35753</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:5">
       <c r="A345">
         <v>1110041</v>
       </c>
@@ -7088,7 +7052,7 @@
         <v>2394267</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:5">
       <c r="A346">
         <v>1110041</v>
       </c>
@@ -7102,10 +7066,10 @@
         <v>219</v>
       </c>
       <c r="E346">
-        <v>3244873</v>
-      </c>
-    </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5">
       <c r="A347">
         <v>1110041</v>
       </c>
@@ -7122,7 +7086,7 @@
         <v>682633</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:5">
       <c r="A348">
         <v>1110041</v>
       </c>
@@ -7139,7 +7103,7 @@
         <v>43260</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:5">
       <c r="A349">
         <v>1110041</v>
       </c>
@@ -7156,7 +7120,7 @@
         <v>951770</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:5">
       <c r="A350">
         <v>1110041</v>
       </c>
@@ -7173,7 +7137,7 @@
         <v>42959</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:5">
       <c r="A351">
         <v>1110042</v>
       </c>
@@ -7190,7 +7154,7 @@
         <v>193742</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:5">
       <c r="A352">
         <v>1110042</v>
       </c>
@@ -7207,7 +7171,7 @@
         <v>233964368</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:5">
       <c r="A353">
         <v>1110042</v>
       </c>
@@ -7221,10 +7185,10 @@
         <v>219</v>
       </c>
       <c r="E353">
-        <v>193576858</v>
-      </c>
-    </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5">
       <c r="A354">
         <v>1110042</v>
       </c>
@@ -7241,7 +7205,7 @@
         <v>16063061</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:5">
       <c r="A355">
         <v>1110042</v>
       </c>
@@ -7255,10 +7219,10 @@
         <v>189</v>
       </c>
       <c r="E355">
-        <v>10151563</v>
-      </c>
-    </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5">
       <c r="A356">
         <v>1110042</v>
       </c>
@@ -7275,7 +7239,7 @@
         <v>22013194</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:5">
       <c r="A357">
         <v>1110042</v>
       </c>
@@ -7292,7 +7256,7 @@
         <v>63498</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:5">
       <c r="A358">
         <v>1110042</v>
       </c>
@@ -7309,7 +7273,7 @@
         <v>166794651</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:5">
       <c r="A359">
         <v>1110042</v>
       </c>
@@ -7326,7 +7290,7 @@
         <v>346170</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:5">
       <c r="A360">
         <v>1110042</v>
       </c>
@@ -7343,7 +7307,7 @@
         <v>-12280499</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:5">
       <c r="A361">
         <v>1110042</v>
       </c>
@@ -7360,7 +7324,7 @@
         <v>1023092</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:5">
       <c r="A362">
         <v>1110043</v>
       </c>
@@ -7377,7 +7341,7 @@
         <v>-2172987</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:5">
       <c r="A363">
         <v>1110043</v>
       </c>
@@ -7394,7 +7358,7 @@
         <v>32743</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:5">
       <c r="A364">
         <v>1110043</v>
       </c>
@@ -7411,7 +7375,7 @@
         <v>1796241</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:5">
       <c r="A365">
         <v>1110043</v>
       </c>
@@ -7428,7 +7392,7 @@
         <v>275674</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:5">
       <c r="A366">
         <v>1110043</v>
       </c>
@@ -7445,7 +7409,7 @@
         <v>23192808</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:5">
       <c r="A367">
         <v>1110043</v>
       </c>
@@ -7462,7 +7426,7 @@
         <v>1919890</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:5">
       <c r="A368">
         <v>1110043</v>
       </c>
@@ -7479,7 +7443,7 @@
         <v>4232</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:5">
       <c r="A369">
         <v>1110043</v>
       </c>
@@ -7496,7 +7460,7 @@
         <v>140117</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:5">
       <c r="A370">
         <v>1110043</v>
       </c>
@@ -7513,7 +7477,7 @@
         <v>2590776</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:5">
       <c r="A371">
         <v>1110043</v>
       </c>
@@ -7530,7 +7494,7 @@
         <v>2562</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:5">
       <c r="A372">
         <v>1110043</v>
       </c>
@@ -7547,7 +7511,7 @@
         <v>7139046</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:5">
       <c r="A373">
         <v>1110043</v>
       </c>
@@ -7564,7 +7528,7 @@
         <v>746152</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:5">
       <c r="A374">
         <v>1110043</v>
       </c>
@@ -7581,7 +7545,7 @@
         <v>108785</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:5">
       <c r="A375">
         <v>1110043</v>
       </c>
@@ -7598,7 +7562,7 @@
         <v>1131287</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:5">
       <c r="A376">
         <v>1110043</v>
       </c>
@@ -7615,7 +7579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:5">
       <c r="A377">
         <v>1110043</v>
       </c>
@@ -7632,7 +7596,7 @@
         <v>95352786</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:5">
       <c r="A378">
         <v>1110043</v>
       </c>
@@ -7649,7 +7613,7 @@
         <v>953810</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:5">
       <c r="A379">
         <v>1110043</v>
       </c>
@@ -7666,7 +7630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:5">
       <c r="A380">
         <v>1110043</v>
       </c>
@@ -7683,7 +7647,7 @@
         <v>13417</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:5">
       <c r="A381">
         <v>1110043</v>
       </c>
@@ -7700,7 +7664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:5">
       <c r="A382">
         <v>1110044</v>
       </c>
@@ -7717,7 +7681,7 @@
         <v>15038471</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:5">
       <c r="A383">
         <v>1110044</v>
       </c>
@@ -7734,7 +7698,7 @@
         <v>1880277</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:5">
       <c r="A384">
         <v>1110044</v>
       </c>
@@ -7751,7 +7715,7 @@
         <v>1623557</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:5">
       <c r="A385">
         <v>1110044</v>
       </c>
@@ -7768,7 +7732,7 @@
         <v>492917</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:5">
       <c r="A386">
         <v>1110044</v>
       </c>
@@ -7782,10 +7746,10 @@
         <v>100</v>
       </c>
       <c r="E386">
-        <v>27512</v>
-      </c>
-    </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5">
       <c r="A387">
         <v>1110044</v>
       </c>
@@ -7802,7 +7766,7 @@
         <v>74228</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:5">
       <c r="A388">
         <v>1110044</v>
       </c>
@@ -7819,7 +7783,7 @@
         <v>49529</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:5">
       <c r="A389">
         <v>1110044</v>
       </c>
@@ -7836,7 +7800,7 @@
         <v>16190</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:5">
       <c r="A390">
         <v>1110044</v>
       </c>
@@ -7853,7 +7817,7 @@
         <v>989905</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:5">
       <c r="A391">
         <v>1110044</v>
       </c>
@@ -7870,7 +7834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:5">
       <c r="A392">
         <v>1110044</v>
       </c>
@@ -7887,7 +7851,7 @@
         <v>54404</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:5">
       <c r="A393">
         <v>1110044</v>
       </c>
@@ -7904,7 +7868,7 @@
         <v>1420875</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:5">
       <c r="A394">
         <v>1110044</v>
       </c>
@@ -7921,7 +7885,7 @@
         <v>2101711</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:5">
       <c r="A395">
         <v>1110044</v>
       </c>
@@ -7938,7 +7902,7 @@
         <v>1371128</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:5">
       <c r="A396">
         <v>1110044</v>
       </c>
@@ -7955,7 +7919,7 @@
         <v>926926</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:5">
       <c r="A397">
         <v>1110044</v>
       </c>
@@ -7972,7 +7936,7 @@
         <v>225803</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:5">
       <c r="A398">
         <v>1110044</v>
       </c>
@@ -7989,7 +7953,7 @@
         <v>42057</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:5">
       <c r="A399">
         <v>1110045</v>
       </c>
@@ -8006,7 +7970,7 @@
         <v>68161662</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:5">
       <c r="A400">
         <v>1110045</v>
       </c>
@@ -8020,10 +7984,10 @@
         <v>219</v>
       </c>
       <c r="E400">
-        <v>1750801</v>
-      </c>
-    </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5">
       <c r="A401">
         <v>1110045</v>
       </c>
@@ -8040,7 +8004,7 @@
         <v>7007326</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:5">
       <c r="A402">
         <v>1110045</v>
       </c>
@@ -8057,7 +8021,7 @@
         <v>1478007</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:5">
       <c r="A403">
         <v>1110045</v>
       </c>
@@ -8071,10 +8035,10 @@
         <v>189</v>
       </c>
       <c r="E403">
-        <v>391886</v>
-      </c>
-    </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5">
       <c r="A404">
         <v>1110045</v>
       </c>
@@ -8091,7 +8055,7 @@
         <v>4923105</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:5">
       <c r="A405">
         <v>1110045</v>
       </c>
@@ -8108,7 +8072,7 @@
         <v>206978</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:5">
       <c r="A406">
         <v>1110046</v>
       </c>
@@ -8125,7 +8089,7 @@
         <v>46781199</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:5">
       <c r="A407">
         <v>1110046</v>
       </c>
@@ -8139,10 +8103,10 @@
         <v>219</v>
       </c>
       <c r="E407">
-        <v>9510509</v>
-      </c>
-    </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5">
       <c r="A408">
         <v>1110046</v>
       </c>
@@ -8159,7 +8123,7 @@
         <v>1903002</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:5">
       <c r="A409">
         <v>1110046</v>
       </c>
@@ -8176,7 +8140,7 @@
         <v>307200</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:5">
       <c r="A410">
         <v>1110046</v>
       </c>
@@ -8190,10 +8154,10 @@
         <v>189</v>
       </c>
       <c r="E410">
-        <v>60213</v>
-      </c>
-    </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5">
       <c r="A411">
         <v>1110046</v>
       </c>
@@ -8210,7 +8174,7 @@
         <v>2949132</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:5">
       <c r="A412">
         <v>1110046</v>
       </c>
@@ -8227,7 +8191,7 @@
         <v>118814</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:5">
       <c r="A413">
         <v>1110047</v>
       </c>
@@ -8244,7 +8208,7 @@
         <v>163960815</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:5">
       <c r="A414">
         <v>1110047</v>
       </c>
@@ -8258,10 +8222,10 @@
         <v>219</v>
       </c>
       <c r="E414">
-        <v>1629935</v>
-      </c>
-    </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5">
       <c r="A415">
         <v>1110047</v>
       </c>
@@ -8278,7 +8242,7 @@
         <v>18350305</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:5">
       <c r="A416">
         <v>1110047</v>
       </c>
@@ -8295,7 +8259,7 @@
         <v>1000582</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:5">
       <c r="A417">
         <v>1110047</v>
       </c>
@@ -8309,10 +8273,10 @@
         <v>189</v>
       </c>
       <c r="E417">
-        <v>697591</v>
-      </c>
-    </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5">
       <c r="A418">
         <v>1110047</v>
       </c>
@@ -8329,7 +8293,7 @@
         <v>10230163</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:5">
       <c r="A419">
         <v>1110047</v>
       </c>
@@ -8346,7 +8310,7 @@
         <v>500817</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:5">
       <c r="A420">
         <v>1110048</v>
       </c>
@@ -8363,7 +8327,7 @@
         <v>3115709</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:5">
       <c r="A421">
         <v>1110048</v>
       </c>
@@ -8380,7 +8344,7 @@
         <v>246341</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:5">
       <c r="A422">
         <v>1110048</v>
       </c>
@@ -8397,7 +8361,7 @@
         <v>344098</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:5">
       <c r="A423">
         <v>1110048</v>
       </c>
@@ -8414,7 +8378,7 @@
         <v>15339</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:5">
       <c r="A424">
         <v>1110049</v>
       </c>
@@ -8431,7 +8395,7 @@
         <v>29952</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:5">
       <c r="A425">
         <v>1110060</v>
       </c>
@@ -8448,7 +8412,7 @@
         <v>47119</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:5">
       <c r="A426">
         <v>1110060</v>
       </c>
@@ -8465,7 +8429,7 @@
         <v>121717</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:5">
       <c r="A427">
         <v>1110061</v>
       </c>
@@ -8482,7 +8446,7 @@
         <v>33208</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:5">
       <c r="A428">
         <v>1110061</v>
       </c>
@@ -8499,7 +8463,7 @@
         <v>391130</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:5">
       <c r="A429">
         <v>1110062</v>
       </c>
@@ -8516,7 +8480,7 @@
         <v>-4437426</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:5">
       <c r="A430">
         <v>1110062</v>
       </c>
@@ -8533,7 +8497,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:5">
       <c r="A431">
         <v>1110062</v>
       </c>
@@ -8550,7 +8514,7 @@
         <v>408299</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:5">
       <c r="A432">
         <v>1110062</v>
       </c>
@@ -8567,7 +8531,7 @@
         <v>1533570</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:5">
       <c r="A433">
         <v>1110062</v>
       </c>
@@ -8584,7 +8548,7 @@
         <v>45212934</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:5">
       <c r="A434">
         <v>1110062</v>
       </c>
@@ -8601,7 +8565,7 @@
         <v>3156446</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:5">
       <c r="A435">
         <v>1110062</v>
       </c>
@@ -8618,7 +8582,7 @@
         <v>342432</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:5">
       <c r="A436">
         <v>1110062</v>
       </c>
@@ -8632,10 +8596,10 @@
         <v>189</v>
       </c>
       <c r="E436">
-        <v>69114</v>
-      </c>
-    </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5">
       <c r="A437">
         <v>1110062</v>
       </c>
@@ -8652,7 +8616,7 @@
         <v>5200932</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:5">
       <c r="A438">
         <v>1110062</v>
       </c>
@@ -8669,7 +8633,7 @@
         <v>788351</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:5">
       <c r="A439">
         <v>1110062</v>
       </c>
@@ -8686,7 +8650,7 @@
         <v>44076296</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:5">
       <c r="A440">
         <v>1110062</v>
       </c>
@@ -8703,7 +8667,7 @@
         <v>-3402830</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:5">
       <c r="A441">
         <v>1110062</v>
       </c>
@@ -8720,7 +8684,7 @@
         <v>222556</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:5">
       <c r="A442">
         <v>1110062</v>
       </c>
@@ -8737,7 +8701,7 @@
         <v>36940</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:5">
       <c r="A443">
         <v>1110062</v>
       </c>
@@ -8754,7 +8718,7 @@
         <v>119181</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:5">
       <c r="A444">
         <v>1110062</v>
       </c>
@@ -8771,7 +8735,7 @@
         <v>68170</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:5">
       <c r="A445">
         <v>1110062</v>
       </c>
@@ -8788,7 +8752,7 @@
         <v>137276</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:5">
       <c r="A446">
         <v>1110062</v>
       </c>
@@ -8805,7 +8769,7 @@
         <v>108299</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:5">
       <c r="A447">
         <v>1110062</v>
       </c>
@@ -8822,7 +8786,7 @@
         <v>10322</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:5">
       <c r="A448">
         <v>1110062</v>
       </c>
@@ -8839,7 +8803,7 @@
         <v>38162</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:5">
       <c r="A449">
         <v>1110062</v>
       </c>
@@ -8856,7 +8820,7 @@
         <v>60891</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:5">
       <c r="A450">
         <v>1110062</v>
       </c>
@@ -8873,7 +8837,7 @@
         <v>124270</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:5">
       <c r="A451">
         <v>1110080</v>
       </c>
@@ -8890,7 +8854,7 @@
         <v>-2497712</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:5">
       <c r="A452">
         <v>1110080</v>
       </c>
@@ -8907,7 +8871,7 @@
         <v>-16000</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:5">
       <c r="A453">
         <v>1110080</v>
       </c>
@@ -8924,7 +8888,7 @@
         <v>-3645590</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:5">
       <c r="A454">
         <v>1110080</v>
       </c>
@@ -8941,7 +8905,7 @@
         <v>270635</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:5">
       <c r="A455">
         <v>1110080</v>
       </c>
@@ -8958,7 +8922,7 @@
         <v>-13294509</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:5">
       <c r="A456">
         <v>1110080</v>
       </c>
@@ -8975,7 +8939,7 @@
         <v>-4525605</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:5">
       <c r="A457">
         <v>1110080</v>
       </c>
@@ -8992,7 +8956,7 @@
         <v>1368395</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:5">
       <c r="A458">
         <v>1110080</v>
       </c>
@@ -9009,7 +8973,7 @@
         <v>17405398</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:5">
       <c r="A459">
         <v>1110080</v>
       </c>
@@ -9026,7 +8990,7 @@
         <v>2905636</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:5">
       <c r="A460">
         <v>1110080</v>
       </c>
@@ -9043,7 +9007,7 @@
         <v>1912741</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:5">
       <c r="A461">
         <v>1110080</v>
       </c>
@@ -9060,7 +9024,7 @@
         <v>137915</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:5">
       <c r="A462">
         <v>1110080</v>
       </c>
@@ -9077,7 +9041,7 @@
         <v>32531</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:5">
       <c r="A463">
         <v>1110080</v>
       </c>
@@ -9094,7 +9058,7 @@
         <v>82578</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:5">
       <c r="A464">
         <v>1110080</v>
       </c>
@@ -9111,7 +9075,7 @@
         <v>59373</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:5">
       <c r="A465">
         <v>1110080</v>
       </c>
@@ -9128,7 +9092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:5">
       <c r="A466">
         <v>1110080</v>
       </c>
@@ -9145,7 +9109,7 @@
         <v>44846</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:5">
       <c r="A467">
         <v>1110080</v>
       </c>
@@ -9162,7 +9126,7 @@
         <v>-22976855</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:5">
       <c r="A468">
         <v>1110080</v>
       </c>
@@ -9179,7 +9143,7 @@
         <v>30270</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:5">
       <c r="A469">
         <v>1110080</v>
       </c>
@@ -9196,7 +9160,7 @@
         <v>920880</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:5">
       <c r="A470">
         <v>1110080</v>
       </c>
@@ -9213,7 +9177,7 @@
         <v>2186424</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:5">
       <c r="A471">
         <v>1110080</v>
       </c>
@@ -9230,7 +9194,7 @@
         <v>5126416</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:5">
       <c r="A472">
         <v>1110080</v>
       </c>
@@ -9247,7 +9211,7 @@
         <v>20273</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:5">
       <c r="A473">
         <v>1110090</v>
       </c>
@@ -9264,7 +9228,7 @@
         <v>48375</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:5">
       <c r="A474">
         <v>1110090</v>
       </c>
@@ -9281,7 +9245,7 @@
         <v>28544</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:5">
       <c r="A475">
         <v>1110091</v>
       </c>
@@ -9298,7 +9262,7 @@
         <v>24816809</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:5">
       <c r="A476">
         <v>1110091</v>
       </c>
@@ -9315,7 +9279,7 @@
         <v>3042383</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:5">
       <c r="A477">
         <v>1110091</v>
       </c>
@@ -9332,7 +9296,7 @@
         <v>2601231</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:5">
       <c r="A478">
         <v>1110091</v>
       </c>
@@ -9349,7 +9313,7 @@
         <v>199988</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:5">
       <c r="A479">
         <v>1110091</v>
       </c>
@@ -9363,10 +9327,10 @@
         <v>100</v>
       </c>
       <c r="E479">
-        <v>194077</v>
-      </c>
-    </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5">
       <c r="A480">
         <v>1110091</v>
       </c>
@@ -9383,7 +9347,7 @@
         <v>114433</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:5">
       <c r="A481">
         <v>1110091</v>
       </c>
@@ -9400,7 +9364,7 @@
         <v>90991</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:5">
       <c r="A482">
         <v>1110091</v>
       </c>
@@ -9417,7 +9381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:5">
       <c r="A483">
         <v>1110091</v>
       </c>
@@ -9434,7 +9398,7 @@
         <v>123885</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:5">
       <c r="A484">
         <v>1110091</v>
       </c>
@@ -9451,7 +9415,7 @@
         <v>268325</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:5">
       <c r="A485">
         <v>1110091</v>
       </c>
@@ -9468,7 +9432,7 @@
         <v>684452</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:5">
       <c r="A486">
         <v>1110091</v>
       </c>
@@ -9485,7 +9449,7 @@
         <v>1701163</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:5">
       <c r="A487">
         <v>1110091</v>
       </c>
@@ -9502,7 +9466,7 @@
         <v>19587</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:5">
       <c r="A488">
         <v>1110091</v>
       </c>
@@ -9519,7 +9483,7 @@
         <v>3412418</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:5">
       <c r="A489">
         <v>1110092</v>
       </c>
@@ -9536,7 +9500,7 @@
         <v>-1988975</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:5">
       <c r="A490">
         <v>1110092</v>
       </c>
@@ -9553,7 +9517,7 @@
         <v>120162</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:5">
       <c r="A491">
         <v>1110092</v>
       </c>
@@ -9570,7 +9534,7 @@
         <v>14153</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:5">
       <c r="A492">
         <v>1110092</v>
       </c>
@@ -9587,7 +9551,7 @@
         <v>18558</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:5">
       <c r="A493">
         <v>1110092</v>
       </c>
@@ -9604,7 +9568,7 @@
         <v>52599</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:5">
       <c r="A494">
         <v>1110092</v>
       </c>
@@ -9621,7 +9585,7 @@
         <v>10224</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:5">
       <c r="A495">
         <v>1110092</v>
       </c>
@@ -9638,7 +9602,7 @@
         <v>970433845</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:5">
       <c r="A496">
         <v>1110092</v>
       </c>
@@ -9655,7 +9619,7 @@
         <v>143612</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:5">
       <c r="A497">
         <v>1110092</v>
       </c>
@@ -9672,7 +9636,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:5">
       <c r="A498">
         <v>1110092</v>
       </c>
@@ -9689,7 +9653,7 @@
         <v>55554</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:5">
       <c r="A499">
         <v>1110092</v>
       </c>
@@ -9706,7 +9670,7 @@
         <v>10258755</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:5">
       <c r="A500">
         <v>1110092</v>
       </c>
@@ -9723,7 +9687,7 @@
         <v>798413</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:5">
       <c r="A501">
         <v>1110092</v>
       </c>
@@ -9740,7 +9704,7 @@
         <v>182067</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:5">
       <c r="A502">
         <v>1110092</v>
       </c>
@@ -9757,7 +9721,7 @@
         <v>36974759</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:5">
       <c r="A503">
         <v>1110092</v>
       </c>
@@ -9774,7 +9738,7 @@
         <v>2983885</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:5">
       <c r="A504">
         <v>1110092</v>
       </c>
@@ -9791,7 +9755,7 @@
         <v>449419</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:5">
       <c r="A505">
         <v>1110092</v>
       </c>
@@ -9808,7 +9772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:5">
       <c r="A506">
         <v>1110092</v>
       </c>
@@ -9825,7 +9789,7 @@
         <v>3841950</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:5">
       <c r="A507">
         <v>1110092</v>
       </c>
@@ -9842,7 +9806,7 @@
         <v>514568</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:5">
       <c r="A508">
         <v>1110092</v>
       </c>
@@ -9859,7 +9823,7 @@
         <v>18452846</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:5">
       <c r="A509">
         <v>1110092</v>
       </c>
@@ -9876,7 +9840,7 @@
         <v>183929</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:5">
       <c r="A510">
         <v>1110092</v>
       </c>
@@ -9893,7 +9857,7 @@
         <v>242209</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:5">
       <c r="A511">
         <v>1110092</v>
       </c>
@@ -9910,7 +9874,7 @@
         <v>13589</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:5">
       <c r="A512">
         <v>1110092</v>
       </c>
@@ -9927,7 +9891,7 @@
         <v>6940</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:5">
       <c r="A513">
         <v>1110092</v>
       </c>
@@ -9944,7 +9908,7 @@
         <v>819108</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:5">
       <c r="A514">
         <v>1110092</v>
       </c>
@@ -9961,7 +9925,7 @@
         <v>111895</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:5">
       <c r="A515">
         <v>1110092</v>
       </c>
@@ -9978,7 +9942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:5">
       <c r="A516">
         <v>1110092</v>
       </c>
@@ -9995,7 +9959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:5">
       <c r="A517">
         <v>1110092</v>
       </c>
@@ -10012,7 +9976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:5">
       <c r="A518">
         <v>1110092</v>
       </c>
@@ -10029,7 +9993,7 @@
         <v>152022</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:5">
       <c r="A519">
         <v>1110092</v>
       </c>
@@ -10046,7 +10010,7 @@
         <v>400854</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:5">
       <c r="A520">
         <v>1110092</v>
       </c>
@@ -10063,7 +10027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:5">
       <c r="A521">
         <v>1110092</v>
       </c>
@@ -10080,7 +10044,7 @@
         <v>397821</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:5">
       <c r="A522">
         <v>1110092</v>
       </c>
@@ -10097,7 +10061,7 @@
         <v>119470</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:5">
       <c r="A523">
         <v>1110093</v>
       </c>
@@ -10114,7 +10078,7 @@
         <v>13957279</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:5">
       <c r="A524">
         <v>1110093</v>
       </c>
@@ -10131,7 +10095,7 @@
         <v>1066652</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:5">
       <c r="A525">
         <v>1110093</v>
       </c>
@@ -10148,7 +10112,7 @@
         <v>1407250</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:5">
       <c r="A526">
         <v>1110093</v>
       </c>
@@ -10165,7 +10129,7 @@
         <v>66557</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:5">
       <c r="A527">
         <v>1110094</v>
       </c>
@@ -10182,7 +10146,7 @@
         <v>7986980</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:5">
       <c r="A528">
         <v>1110094</v>
       </c>
@@ -10199,7 +10163,7 @@
         <v>1342228</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:5">
       <c r="A529">
         <v>1110094</v>
       </c>
@@ -10216,7 +10180,7 @@
         <v>942675</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:5">
       <c r="A530">
         <v>1110094</v>
       </c>
@@ -10233,7 +10197,7 @@
         <v>44343</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:5">
       <c r="A531">
         <v>1110100</v>
       </c>
@@ -10250,7 +10214,7 @@
         <v>1201828</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:5">
       <c r="A532">
         <v>1110100</v>
       </c>
@@ -10267,7 +10231,7 @@
         <v>1018055</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:5">
       <c r="A533">
         <v>1110100</v>
       </c>
@@ -10281,10 +10245,10 @@
         <v>100</v>
       </c>
       <c r="E533">
-        <v>624653</v>
-      </c>
-    </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5">
       <c r="A534">
         <v>1110101</v>
       </c>
@@ -10301,7 +10265,7 @@
         <v>4924995</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:5">
       <c r="A535">
         <v>1110101</v>
       </c>
@@ -10318,7 +10282,7 @@
         <v>6159118</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:5">
       <c r="A536">
         <v>1110101</v>
       </c>
@@ -10335,7 +10299,7 @@
         <v>5287285</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:5">
       <c r="A537">
         <v>1110101</v>
       </c>
@@ -10352,7 +10316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:5">
       <c r="A538">
         <v>1110101</v>
       </c>
@@ -10369,7 +10333,7 @@
         <v>19815</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:5">
       <c r="A539">
         <v>1110101</v>
       </c>
@@ -10386,7 +10350,7 @@
         <v>153420</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:5">
       <c r="A540">
         <v>1110102</v>
       </c>
@@ -10403,7 +10367,7 @@
         <v>4526999</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:5">
       <c r="A541">
         <v>1110102</v>
       </c>
@@ -10420,7 +10384,7 @@
         <v>490413</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:5">
       <c r="A542">
         <v>1110102</v>
       </c>
@@ -10437,7 +10401,7 @@
         <v>968482</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:5">
       <c r="A543">
         <v>1110102</v>
       </c>
@@ -10451,10 +10415,10 @@
         <v>100</v>
       </c>
       <c r="E543">
-        <v>1018818</v>
-      </c>
-    </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5">
       <c r="A544">
         <v>1110102</v>
       </c>
@@ -10471,7 +10435,7 @@
         <v>24150</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:5">
       <c r="A545">
         <v>1110102</v>
       </c>
@@ -10488,7 +10452,7 @@
         <v>27267</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:5">
       <c r="A546">
         <v>1110121</v>
       </c>
@@ -10505,7 +10469,7 @@
         <v>29438633</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:5">
       <c r="A547">
         <v>1110121</v>
       </c>
@@ -10522,7 +10486,7 @@
         <v>2839845</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:5">
       <c r="A548">
         <v>1110121</v>
       </c>
@@ -10539,7 +10503,7 @@
         <v>3017610</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:5">
       <c r="A549">
         <v>1110121</v>
       </c>
@@ -10556,7 +10520,7 @@
         <v>228708</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:5">
       <c r="A550">
         <v>1110121</v>
       </c>
@@ -10570,10 +10534,10 @@
         <v>100</v>
       </c>
       <c r="E550">
-        <v>167907</v>
-      </c>
-    </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5">
       <c r="A551">
         <v>1110121</v>
       </c>
@@ -10590,7 +10554,7 @@
         <v>20650</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:5">
       <c r="A552">
         <v>1110121</v>
       </c>
@@ -10607,7 +10571,7 @@
         <v>134422</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:5">
       <c r="A553">
         <v>1110121</v>
       </c>
@@ -10624,7 +10588,7 @@
         <v>2446</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:5">
       <c r="A554">
         <v>1110121</v>
       </c>
@@ -10641,7 +10605,7 @@
         <v>183353</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:5">
       <c r="A555">
         <v>1110121</v>
       </c>
@@ -10658,7 +10622,7 @@
         <v>254643</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:5">
       <c r="A556">
         <v>1110122</v>
       </c>
@@ -10675,7 +10639,7 @@
         <v>86385</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:5">
       <c r="A557">
         <v>1110122</v>
       </c>
@@ -10689,10 +10653,10 @@
         <v>189</v>
       </c>
       <c r="E557">
-        <v>57976</v>
-      </c>
-    </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5">
       <c r="A558">
         <v>1110122</v>
       </c>
@@ -10709,7 +10673,7 @@
         <v>9440</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:5">
       <c r="A559">
         <v>1110122</v>
       </c>
@@ -10726,7 +10690,7 @@
         <v>5189</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:5">
       <c r="A560">
         <v>1110122</v>
       </c>
@@ -10743,7 +10707,7 @@
         <v>46979</v>
       </c>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:5">
       <c r="A561">
         <v>1110122</v>
       </c>
@@ -10760,7 +10724,7 @@
         <v>82249</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:5">
       <c r="A562">
         <v>1110122</v>
       </c>
@@ -10777,7 +10741,7 @@
         <v>3720413</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:5">
       <c r="A563">
         <v>1110122</v>
       </c>
@@ -10794,7 +10758,7 @@
         <v>17746035</v>
       </c>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:5">
       <c r="A564">
         <v>1110122</v>
       </c>
@@ -10811,7 +10775,7 @@
         <v>1981152</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:5">
       <c r="A565">
         <v>1110122</v>
       </c>
@@ -10828,7 +10792,7 @@
         <v>90354</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:5">
       <c r="A566">
         <v>1110122</v>
       </c>
@@ -10845,7 +10809,7 @@
         <v>1771226</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:5">
       <c r="A567">
         <v>1110123</v>
       </c>
@@ -10862,7 +10826,7 @@
         <v>132159</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:5">
       <c r="A568">
         <v>1110123</v>
       </c>
@@ -10876,10 +10840,10 @@
         <v>189</v>
       </c>
       <c r="E568">
-        <v>60615</v>
-      </c>
-    </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="569" spans="1:5">
       <c r="A569">
         <v>1110123</v>
       </c>
@@ -10896,7 +10860,7 @@
         <v>931632</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:5">
       <c r="A570">
         <v>1110123</v>
       </c>
@@ -10913,7 +10877,7 @@
         <v>2615750</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:5">
       <c r="A571">
         <v>1110123</v>
       </c>
@@ -10930,7 +10894,7 @@
         <v>22855570</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:5">
       <c r="A572">
         <v>1110123</v>
       </c>
@@ -10947,7 +10911,7 @@
         <v>2248601</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:5">
       <c r="A573">
         <v>1110123</v>
       </c>
@@ -10964,7 +10928,7 @@
         <v>111909</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:5">
       <c r="A574">
         <v>1110123</v>
       </c>
@@ -10981,7 +10945,7 @@
         <v>2629034</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:5">
       <c r="A575">
         <v>1110123</v>
       </c>
@@ -10998,7 +10962,7 @@
         <v>10329</v>
       </c>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:5">
       <c r="A576">
         <v>1110124</v>
       </c>
@@ -11015,7 +10979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:5">
       <c r="A577">
         <v>1110124</v>
       </c>
@@ -11032,7 +10996,7 @@
         <v>157362</v>
       </c>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:5">
       <c r="A578">
         <v>1110124</v>
       </c>
@@ -11046,10 +11010,10 @@
         <v>189</v>
       </c>
       <c r="E578">
-        <v>229351</v>
-      </c>
-    </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="579" spans="1:5">
       <c r="A579">
         <v>1110124</v>
       </c>
@@ -11066,7 +11030,7 @@
         <v>3239</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:5">
       <c r="A580">
         <v>1110124</v>
       </c>
@@ -11083,7 +11047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:5">
       <c r="A581">
         <v>1110124</v>
       </c>
@@ -11100,7 +11064,7 @@
         <v>332704</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:5">
       <c r="A582">
         <v>1110124</v>
       </c>
@@ -11117,7 +11081,7 @@
         <v>24259058</v>
       </c>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:5">
       <c r="A583">
         <v>1110124</v>
       </c>
@@ -11134,7 +11098,7 @@
         <v>2486504</v>
       </c>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:5">
       <c r="A584">
         <v>1110124</v>
       </c>
@@ -11151,7 +11115,7 @@
         <v>125567</v>
       </c>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:5">
       <c r="A585">
         <v>1110124</v>
       </c>
@@ -11168,7 +11132,7 @@
         <v>2695341</v>
       </c>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:5">
       <c r="A586">
         <v>1110125</v>
       </c>
@@ -11185,7 +11149,7 @@
         <v>62952</v>
       </c>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:5">
       <c r="A587">
         <v>1110125</v>
       </c>
@@ -11202,7 +11166,7 @@
         <v>15135016</v>
       </c>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:5">
       <c r="A588">
         <v>1110125</v>
       </c>
@@ -11219,7 +11183,7 @@
         <v>1042942</v>
       </c>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:5">
       <c r="A589">
         <v>1110125</v>
       </c>
@@ -11236,7 +11200,7 @@
         <v>1637031</v>
       </c>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:5">
       <c r="A590">
         <v>1110125</v>
       </c>
@@ -11253,7 +11217,7 @@
         <v>83152</v>
       </c>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:5">
       <c r="A591">
         <v>1120001</v>
       </c>
@@ -11270,7 +11234,7 @@
         <v>9803301</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:5">
       <c r="A592">
         <v>1120002</v>
       </c>
@@ -11287,7 +11251,7 @@
         <v>19207547</v>
       </c>
     </row>
-    <row r="593" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:5">
       <c r="A593">
         <v>1120002</v>
       </c>
@@ -11304,7 +11268,7 @@
         <v>132628</v>
       </c>
     </row>
-    <row r="594" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:5">
       <c r="A594">
         <v>1200001</v>
       </c>
@@ -11321,7 +11285,7 @@
         <v>17138829</v>
       </c>
     </row>
-    <row r="595" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:5">
       <c r="A595">
         <v>1200001</v>
       </c>
@@ -11338,7 +11302,7 @@
         <v>1386549</v>
       </c>
     </row>
-    <row r="596" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="596" spans="1:5">
       <c r="A596">
         <v>1200001</v>
       </c>
@@ -11352,10 +11316,10 @@
         <v>189</v>
       </c>
       <c r="E596">
-        <v>657964</v>
-      </c>
-    </row>
-    <row r="597" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="597" spans="1:5">
       <c r="A597">
         <v>1200001</v>
       </c>
@@ -11372,7 +11336,7 @@
         <v>1557469</v>
       </c>
     </row>
-    <row r="598" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:5">
       <c r="A598">
         <v>1200001</v>
       </c>
@@ -11389,7 +11353,7 @@
         <v>77080</v>
       </c>
     </row>
-    <row r="599" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:5">
       <c r="A599">
         <v>1210001</v>
       </c>
@@ -11406,7 +11370,7 @@
         <v>-28023</v>
       </c>
     </row>
-    <row r="600" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:5">
       <c r="A600">
         <v>1210001</v>
       </c>
@@ -11423,7 +11387,7 @@
         <v>12605</v>
       </c>
     </row>
-    <row r="601" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:5">
       <c r="A601">
         <v>1210002</v>
       </c>
@@ -11440,7 +11404,7 @@
         <v>13078441</v>
       </c>
     </row>
-    <row r="602" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:5">
       <c r="A602">
         <v>1210002</v>
       </c>
@@ -11457,7 +11421,7 @@
         <v>1042868</v>
       </c>
     </row>
-    <row r="603" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:5">
       <c r="A603">
         <v>1210002</v>
       </c>
@@ -11474,7 +11438,7 @@
         <v>11649</v>
       </c>
     </row>
-    <row r="604" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:5">
       <c r="A604">
         <v>1210002</v>
       </c>
@@ -11491,7 +11455,7 @@
         <v>172360</v>
       </c>
     </row>
-    <row r="605" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:5">
       <c r="A605">
         <v>1210002</v>
       </c>
@@ -11505,10 +11469,10 @@
         <v>189</v>
       </c>
       <c r="E605">
-        <v>465749</v>
-      </c>
-    </row>
-    <row r="606" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="606" spans="1:5">
       <c r="A606">
         <v>1210002</v>
       </c>
@@ -11525,7 +11489,7 @@
         <v>1554387</v>
       </c>
     </row>
-    <row r="607" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:5">
       <c r="A607">
         <v>1210002</v>
       </c>
@@ -11542,7 +11506,7 @@
         <v>22201</v>
       </c>
     </row>
-    <row r="608" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:5">
       <c r="A608">
         <v>1210002</v>
       </c>
@@ -11559,7 +11523,7 @@
         <v>4517406</v>
       </c>
     </row>
-    <row r="609" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:5">
       <c r="A609">
         <v>1210002</v>
       </c>
@@ -11576,7 +11540,7 @@
         <v>64015</v>
       </c>
     </row>
-    <row r="610" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:5">
       <c r="A610">
         <v>1210002</v>
       </c>
@@ -11593,7 +11557,7 @@
         <v>102850</v>
       </c>
     </row>
-    <row r="611" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:5">
       <c r="A611">
         <v>1210002</v>
       </c>
@@ -11610,7 +11574,7 @@
         <v>60604</v>
       </c>
     </row>
-    <row r="612" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:5">
       <c r="A612">
         <v>1210002</v>
       </c>
@@ -11627,7 +11591,7 @@
         <v>611003</v>
       </c>
     </row>
-    <row r="613" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:5">
       <c r="A613">
         <v>1210002</v>
       </c>
@@ -11644,7 +11608,7 @@
         <v>5085</v>
       </c>
     </row>
-    <row r="614" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:5">
       <c r="A614">
         <v>1210003</v>
       </c>
@@ -11661,7 +11625,7 @@
         <v>11180118</v>
       </c>
     </row>
-    <row r="615" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:5">
       <c r="A615">
         <v>1210003</v>
       </c>
@@ -11678,7 +11642,7 @@
         <v>926055</v>
       </c>
     </row>
-    <row r="616" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:5">
       <c r="A616">
         <v>1210003</v>
       </c>
@@ -11695,7 +11659,7 @@
         <v>1297918</v>
       </c>
     </row>
-    <row r="617" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:5">
       <c r="A617">
         <v>1210003</v>
       </c>
@@ -11712,7 +11676,7 @@
         <v>36834</v>
       </c>
     </row>
-    <row r="618" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:5">
       <c r="A618">
         <v>1210003</v>
       </c>
@@ -11729,7 +11693,7 @@
         <v>202157</v>
       </c>
     </row>
-    <row r="619" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:5">
       <c r="A619">
         <v>1210003</v>
       </c>
@@ -11743,10 +11707,10 @@
         <v>100</v>
       </c>
       <c r="E619">
-        <v>109828</v>
-      </c>
-    </row>
-    <row r="620" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="620" spans="1:5">
       <c r="A620">
         <v>1210003</v>
       </c>
@@ -11763,7 +11727,7 @@
         <v>94950</v>
       </c>
     </row>
-    <row r="621" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:5">
       <c r="A621">
         <v>1210003</v>
       </c>
@@ -11780,7 +11744,7 @@
         <v>4866611</v>
       </c>
     </row>
-    <row r="622" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:5">
       <c r="A622">
         <v>1210003</v>
       </c>
@@ -11797,7 +11761,7 @@
         <v>54302</v>
       </c>
     </row>
-    <row r="623" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:5">
       <c r="A623">
         <v>1210003</v>
       </c>
@@ -11814,7 +11778,7 @@
         <v>417906</v>
       </c>
     </row>
-    <row r="624" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:5">
       <c r="A624">
         <v>1210003</v>
       </c>
@@ -11831,7 +11795,7 @@
         <v>178709</v>
       </c>
     </row>
-    <row r="625" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:5">
       <c r="A625">
         <v>1210003</v>
       </c>
@@ -11848,7 +11812,7 @@
         <v>119783</v>
       </c>
     </row>
-    <row r="626" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:5">
       <c r="A626">
         <v>1210003</v>
       </c>
@@ -11865,7 +11829,7 @@
         <v>77505</v>
       </c>
     </row>
-    <row r="627" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:5">
       <c r="A627">
         <v>1210003</v>
       </c>
@@ -11882,7 +11846,7 @@
         <v>5400353</v>
       </c>
     </row>
-    <row r="628" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:5">
       <c r="A628">
         <v>1210003</v>
       </c>
@@ -11899,7 +11863,7 @@
         <v>3148350</v>
       </c>
     </row>
-    <row r="629" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:5">
       <c r="A629">
         <v>1210003</v>
       </c>
@@ -11916,7 +11880,7 @@
         <v>1963026</v>
       </c>
     </row>
-    <row r="630" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:5">
       <c r="A630">
         <v>1210003</v>
       </c>
@@ -11933,7 +11897,7 @@
         <v>1574766</v>
       </c>
     </row>
-    <row r="631" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:5">
       <c r="A631">
         <v>1210003</v>
       </c>
@@ -11950,7 +11914,7 @@
         <v>40443355</v>
       </c>
     </row>
-    <row r="632" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:5">
       <c r="A632">
         <v>1210003</v>
       </c>
@@ -11967,7 +11931,7 @@
         <v>7071615</v>
       </c>
     </row>
-    <row r="633" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:5">
       <c r="A633">
         <v>1210003</v>
       </c>
@@ -11984,7 +11948,7 @@
         <v>22040</v>
       </c>
     </row>
-    <row r="634" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:5">
       <c r="A634">
         <v>1210003</v>
       </c>
@@ -12001,7 +11965,7 @@
         <v>986082</v>
       </c>
     </row>
-    <row r="635" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:5">
       <c r="A635">
         <v>1210003</v>
       </c>
@@ -12018,7 +11982,7 @@
         <v>41418660</v>
       </c>
     </row>
-    <row r="636" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:5">
       <c r="A636">
         <v>1210003</v>
       </c>
@@ -12035,7 +11999,7 @@
         <v>19683204</v>
       </c>
     </row>
-    <row r="637" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:5">
       <c r="A637">
         <v>1210003</v>
       </c>
@@ -12052,7 +12016,7 @@
         <v>3797199</v>
       </c>
     </row>
-    <row r="638" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:5">
       <c r="A638">
         <v>1210003</v>
       </c>
@@ -12069,7 +12033,7 @@
         <v>1950982</v>
       </c>
     </row>
-    <row r="639" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:5">
       <c r="A639">
         <v>1210003</v>
       </c>
@@ -12086,7 +12050,7 @@
         <v>-36505417</v>
       </c>
     </row>
-    <row r="640" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:5">
       <c r="A640">
         <v>1210003</v>
       </c>
@@ -12103,7 +12067,7 @@
         <v>8400340</v>
       </c>
     </row>
-    <row r="641" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:5">
       <c r="A641">
         <v>1210003</v>
       </c>
@@ -12120,7 +12084,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="642" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:5">
       <c r="A642">
         <v>1210003</v>
       </c>
@@ -12137,7 +12101,7 @@
         <v>82886</v>
       </c>
     </row>
-    <row r="643" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:5">
       <c r="A643">
         <v>1210003</v>
       </c>
@@ -12154,7 +12118,7 @@
         <v>278973</v>
       </c>
     </row>
-    <row r="644" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:5">
       <c r="A644">
         <v>1210003</v>
       </c>
@@ -12171,7 +12135,7 @@
         <v>142943</v>
       </c>
     </row>
-    <row r="645" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:5">
       <c r="A645">
         <v>1210003</v>
       </c>
@@ -12188,7 +12152,7 @@
         <v>256659</v>
       </c>
     </row>
-    <row r="646" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:5">
       <c r="A646">
         <v>1210003</v>
       </c>
@@ -12205,7 +12169,7 @@
         <v>17559570</v>
       </c>
     </row>
-    <row r="647" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:5">
       <c r="A647">
         <v>1210003</v>
       </c>
@@ -12222,7 +12186,7 @@
         <v>3057956</v>
       </c>
     </row>
-    <row r="648" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:5">
       <c r="A648">
         <v>1210003</v>
       </c>
@@ -12239,7 +12203,7 @@
         <v>1965789</v>
       </c>
     </row>
-    <row r="649" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:5">
       <c r="A649">
         <v>1210003</v>
       </c>
@@ -12256,7 +12220,7 @@
         <v>8125</v>
       </c>
     </row>
-    <row r="650" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:5">
       <c r="A650">
         <v>1210003</v>
       </c>
@@ -12273,7 +12237,7 @@
         <v>967974</v>
       </c>
     </row>
-    <row r="651" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:5">
       <c r="A651">
         <v>1210003</v>
       </c>
@@ -12290,7 +12254,7 @@
         <v>161926</v>
       </c>
     </row>
-    <row r="652" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:5">
       <c r="A652">
         <v>1210003</v>
       </c>
@@ -12307,7 +12271,7 @@
         <v>126542</v>
       </c>
     </row>
-    <row r="653" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:5">
       <c r="A653">
         <v>1210004</v>
       </c>
@@ -12324,7 +12288,7 @@
         <v>7687837</v>
       </c>
     </row>
-    <row r="654" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:5">
       <c r="A654">
         <v>1210004</v>
       </c>
@@ -12341,7 +12305,7 @@
         <v>656779</v>
       </c>
     </row>
-    <row r="655" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:5">
       <c r="A655">
         <v>1210004</v>
       </c>
@@ -12358,7 +12322,7 @@
         <v>435104</v>
       </c>
     </row>
-    <row r="656" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:5">
       <c r="A656">
         <v>1210004</v>
       </c>
@@ -12375,7 +12339,7 @@
         <v>36142</v>
       </c>
     </row>
-    <row r="657" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:5">
       <c r="A657">
         <v>1210005</v>
       </c>
@@ -12392,7 +12356,7 @@
         <v>10170656</v>
       </c>
     </row>
-    <row r="658" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:5">
       <c r="A658">
         <v>1210005</v>
       </c>
@@ -12409,7 +12373,7 @@
         <v>991099</v>
       </c>
     </row>
-    <row r="659" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:5">
       <c r="A659">
         <v>1210005</v>
       </c>
@@ -12426,7 +12390,7 @@
         <v>71502</v>
       </c>
     </row>
-    <row r="660" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:5">
       <c r="A660">
         <v>1210005</v>
       </c>
@@ -12440,10 +12404,10 @@
         <v>189</v>
       </c>
       <c r="E660">
-        <v>1122728</v>
-      </c>
-    </row>
-    <row r="661" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="661" spans="1:5">
       <c r="A661">
         <v>1210005</v>
       </c>
@@ -12460,7 +12424,7 @@
         <v>1089865</v>
       </c>
     </row>
-    <row r="662" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:5">
       <c r="A662">
         <v>1210005</v>
       </c>
@@ -12477,7 +12441,7 @@
         <v>369037</v>
       </c>
     </row>
-    <row r="663" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:5">
       <c r="A663">
         <v>1210005</v>
       </c>
@@ -12494,7 +12458,7 @@
         <v>886536</v>
       </c>
     </row>
-    <row r="664" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:5">
       <c r="A664">
         <v>1210005</v>
       </c>
@@ -12511,7 +12475,7 @@
         <v>54977</v>
       </c>
     </row>
-    <row r="665" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:5">
       <c r="A665">
         <v>1210005</v>
       </c>
@@ -12528,7 +12492,7 @@
         <v>54509</v>
       </c>
     </row>
-    <row r="666" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:5">
       <c r="A666">
         <v>1210005</v>
       </c>
@@ -12545,7 +12509,7 @@
         <v>18799</v>
       </c>
     </row>
-    <row r="667" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:5">
       <c r="A667">
         <v>1210006</v>
       </c>
@@ -12562,7 +12526,7 @@
         <v>27552946</v>
       </c>
     </row>
-    <row r="668" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:5">
       <c r="A668">
         <v>1210006</v>
       </c>
@@ -12579,7 +12543,7 @@
         <v>2343131</v>
       </c>
     </row>
-    <row r="669" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:5">
       <c r="A669">
         <v>1210006</v>
       </c>
@@ -12596,7 +12560,7 @@
         <v>34399</v>
       </c>
     </row>
-    <row r="670" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:5">
       <c r="A670">
         <v>1210006</v>
       </c>
@@ -12613,7 +12577,7 @@
         <v>98079</v>
       </c>
     </row>
-    <row r="671" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="671" spans="1:5">
       <c r="A671">
         <v>1210006</v>
       </c>
@@ -12630,7 +12594,7 @@
         <v>3132746</v>
       </c>
     </row>
-    <row r="672" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="672" spans="1:5">
       <c r="A672">
         <v>1210006</v>
       </c>
@@ -12647,7 +12611,7 @@
         <v>310318</v>
       </c>
     </row>
-    <row r="673" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="673" spans="1:5">
       <c r="A673">
         <v>1210006</v>
       </c>
@@ -12664,7 +12628,7 @@
         <v>141672</v>
       </c>
     </row>
-    <row r="674" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:5">
       <c r="A674">
         <v>1210006</v>
       </c>
@@ -12681,7 +12645,7 @@
         <v>10252</v>
       </c>
     </row>
-    <row r="675" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="675" spans="1:5">
       <c r="A675">
         <v>1210006</v>
       </c>
@@ -12698,7 +12662,7 @@
         <v>87207</v>
       </c>
     </row>
-    <row r="676" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="676" spans="1:5">
       <c r="A676">
         <v>1210006</v>
       </c>
@@ -12715,7 +12679,7 @@
         <v>36194</v>
       </c>
     </row>
-    <row r="677" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="677" spans="1:5">
       <c r="A677">
         <v>1210006</v>
       </c>
@@ -12732,7 +12696,7 @@
         <v>381765</v>
       </c>
     </row>
-    <row r="678" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:5">
       <c r="A678">
         <v>1210006</v>
       </c>
@@ -12749,7 +12713,7 @@
         <v>23184</v>
       </c>
     </row>
-    <row r="679" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="679" spans="1:5">
       <c r="A679">
         <v>1210006</v>
       </c>
@@ -12766,7 +12730,7 @@
         <v>50003</v>
       </c>
     </row>
-    <row r="680" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="680" spans="1:5">
       <c r="A680">
         <v>1210006</v>
       </c>
@@ -12783,7 +12747,7 @@
         <v>158414</v>
       </c>
     </row>
-    <row r="681" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="681" spans="1:5">
       <c r="A681">
         <v>1210006</v>
       </c>
@@ -12800,7 +12764,7 @@
         <v>42085</v>
       </c>
     </row>
-    <row r="682" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="682" spans="1:5">
       <c r="A682">
         <v>1210006</v>
       </c>
@@ -12817,7 +12781,7 @@
         <v>1645795</v>
       </c>
     </row>
-    <row r="683" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="683" spans="1:5">
       <c r="A683">
         <v>1210006</v>
       </c>
@@ -12834,7 +12798,7 @@
         <v>93174</v>
       </c>
     </row>
-    <row r="684" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="684" spans="1:5">
       <c r="A684">
         <v>1210006</v>
       </c>
@@ -12851,7 +12815,7 @@
         <v>4428</v>
       </c>
     </row>
-    <row r="685" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="685" spans="1:5">
       <c r="A685">
         <v>1210006</v>
       </c>
@@ -12868,7 +12832,7 @@
         <v>112915</v>
       </c>
     </row>
-    <row r="686" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:5">
       <c r="A686">
         <v>1210006</v>
       </c>
@@ -12885,7 +12849,7 @@
         <v>1655533</v>
       </c>
     </row>
-    <row r="687" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:5">
       <c r="A687">
         <v>1210006</v>
       </c>
@@ -12902,7 +12866,7 @@
         <v>65786</v>
       </c>
     </row>
-    <row r="688" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:5">
       <c r="A688">
         <v>1210006</v>
       </c>
@@ -12919,7 +12883,7 @@
         <v>91507</v>
       </c>
     </row>
-    <row r="689" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="689" spans="1:5">
       <c r="A689">
         <v>1210007</v>
       </c>
@@ -12936,7 +12900,7 @@
         <v>-3155295</v>
       </c>
     </row>
-    <row r="690" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="690" spans="1:5">
       <c r="A690">
         <v>1210007</v>
       </c>
@@ -12953,7 +12917,7 @@
         <v>25572253</v>
       </c>
     </row>
-    <row r="691" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:5">
       <c r="A691">
         <v>1210007</v>
       </c>
@@ -12970,7 +12934,7 @@
         <v>2301082</v>
       </c>
     </row>
-    <row r="692" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="692" spans="1:5">
       <c r="A692">
         <v>1210007</v>
       </c>
@@ -12987,7 +12951,7 @@
         <v>17113</v>
       </c>
     </row>
-    <row r="693" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:5">
       <c r="A693">
         <v>1210007</v>
       </c>
@@ -13004,7 +12968,7 @@
         <v>417788</v>
       </c>
     </row>
-    <row r="694" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="694" spans="1:5">
       <c r="A694">
         <v>1210007</v>
       </c>
@@ -13018,10 +12982,10 @@
         <v>189</v>
       </c>
       <c r="E694">
-        <v>53192</v>
-      </c>
-    </row>
-    <row r="695" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="695" spans="1:5">
       <c r="A695">
         <v>1210007</v>
       </c>
@@ -13038,7 +13002,7 @@
         <v>2868918</v>
       </c>
     </row>
-    <row r="696" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:5">
       <c r="A696">
         <v>1210007</v>
       </c>
@@ -13055,7 +13019,7 @@
         <v>378051</v>
       </c>
     </row>
-    <row r="697" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:5">
       <c r="A697">
         <v>1210007</v>
       </c>
@@ -13072,7 +13036,7 @@
         <v>8666</v>
       </c>
     </row>
-    <row r="698" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="698" spans="1:5">
       <c r="A698">
         <v>1210007</v>
       </c>
@@ -13089,7 +13053,7 @@
         <v>147776</v>
       </c>
     </row>
-    <row r="699" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="699" spans="1:5">
       <c r="A699">
         <v>1210007</v>
       </c>
@@ -13106,7 +13070,7 @@
         <v>6008</v>
       </c>
     </row>
-    <row r="700" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="700" spans="1:5">
       <c r="A700">
         <v>1210007</v>
       </c>
@@ -13123,7 +13087,7 @@
         <v>166722</v>
       </c>
     </row>
-    <row r="701" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="701" spans="1:5">
       <c r="A701">
         <v>1210007</v>
       </c>
@@ -13140,7 +13104,7 @@
         <v>407272</v>
       </c>
     </row>
-    <row r="702" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="702" spans="1:5">
       <c r="A702">
         <v>1210007</v>
       </c>
@@ -13157,7 +13121,7 @@
         <v>371545</v>
       </c>
     </row>
-    <row r="703" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="703" spans="1:5">
       <c r="A703">
         <v>1210007</v>
       </c>
@@ -13174,7 +13138,7 @@
         <v>154847</v>
       </c>
     </row>
-    <row r="704" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="704" spans="1:5">
       <c r="A704">
         <v>1210007</v>
       </c>
@@ -13191,7 +13155,7 @@
         <v>84543</v>
       </c>
     </row>
-    <row r="705" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="705" spans="1:5">
       <c r="A705">
         <v>1210007</v>
       </c>
@@ -13208,7 +13172,7 @@
         <v>19858</v>
       </c>
     </row>
-    <row r="706" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="706" spans="1:5">
       <c r="A706">
         <v>1210007</v>
       </c>
@@ -13225,7 +13189,7 @@
         <v>136651</v>
       </c>
     </row>
-    <row r="707" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="707" spans="1:5">
       <c r="A707">
         <v>1210007</v>
       </c>
@@ -13242,7 +13206,7 @@
         <v>6579</v>
       </c>
     </row>
-    <row r="708" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="708" spans="1:5">
       <c r="A708">
         <v>1210007</v>
       </c>
@@ -13259,7 +13223,7 @@
         <v>251628</v>
       </c>
     </row>
-    <row r="709" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="709" spans="1:5">
       <c r="A709">
         <v>1210007</v>
       </c>
@@ -13276,7 +13240,7 @@
         <v>203527</v>
       </c>
     </row>
-    <row r="710" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="710" spans="1:5">
       <c r="A710">
         <v>1210008</v>
       </c>
@@ -13293,7 +13257,7 @@
         <v>24888060</v>
       </c>
     </row>
-    <row r="711" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="711" spans="1:5">
       <c r="A711">
         <v>1210008</v>
       </c>
@@ -13307,10 +13271,10 @@
         <v>219</v>
       </c>
       <c r="E711">
-        <v>24152079</v>
-      </c>
-    </row>
-    <row r="712" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="712" spans="1:5">
       <c r="A712">
         <v>1210008</v>
       </c>
@@ -13327,7 +13291,7 @@
         <v>2416503</v>
       </c>
     </row>
-    <row r="713" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="713" spans="1:5">
       <c r="A713">
         <v>1210008</v>
       </c>
@@ -13344,7 +13308,7 @@
         <v>40883</v>
       </c>
     </row>
-    <row r="714" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="714" spans="1:5">
       <c r="A714">
         <v>1210008</v>
       </c>
@@ -13361,7 +13325,7 @@
         <v>204012</v>
       </c>
     </row>
-    <row r="715" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="715" spans="1:5">
       <c r="A715">
         <v>1210008</v>
       </c>
@@ -13375,10 +13339,10 @@
         <v>189</v>
       </c>
       <c r="E715">
-        <v>937448</v>
-      </c>
-    </row>
-    <row r="716" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="716" spans="1:5">
       <c r="A716">
         <v>1210008</v>
       </c>
@@ -13395,7 +13359,7 @@
         <v>3345234</v>
       </c>
     </row>
-    <row r="717" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="717" spans="1:5">
       <c r="A717">
         <v>1210008</v>
       </c>
@@ -13412,7 +13376,7 @@
         <v>2354918</v>
       </c>
     </row>
-    <row r="718" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="718" spans="1:5">
       <c r="A718">
         <v>1210008</v>
       </c>
@@ -13429,7 +13393,7 @@
         <v>135586</v>
       </c>
     </row>
-    <row r="719" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="719" spans="1:5">
       <c r="A719">
         <v>1210009</v>
       </c>
@@ -13446,7 +13410,7 @@
         <v>4519259</v>
       </c>
     </row>
-    <row r="720" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="720" spans="1:5">
       <c r="A720">
         <v>1210009</v>
       </c>
@@ -13460,10 +13424,10 @@
         <v>219</v>
       </c>
       <c r="E720">
-        <v>238416</v>
-      </c>
-    </row>
-    <row r="721" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="721" spans="1:5">
       <c r="A721">
         <v>1210009</v>
       </c>
@@ -13480,7 +13444,7 @@
         <v>225697</v>
       </c>
     </row>
-    <row r="722" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="722" spans="1:5">
       <c r="A722">
         <v>1210009</v>
       </c>
@@ -13497,7 +13461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="723" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="723" spans="1:5">
       <c r="A723">
         <v>1210009</v>
       </c>
@@ -13514,7 +13478,7 @@
         <v>666465</v>
       </c>
     </row>
-    <row r="724" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="724" spans="1:5">
       <c r="A724">
         <v>1210009</v>
       </c>
@@ -13531,7 +13495,7 @@
         <v>15496</v>
       </c>
     </row>
-    <row r="725" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="725" spans="1:5">
       <c r="A725">
         <v>1210010</v>
       </c>
@@ -13548,7 +13512,7 @@
         <v>15886949</v>
       </c>
     </row>
-    <row r="726" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="726" spans="1:5">
       <c r="A726">
         <v>1210010</v>
       </c>
@@ -13562,10 +13526,10 @@
         <v>219</v>
       </c>
       <c r="E726">
-        <v>81179</v>
-      </c>
-    </row>
-    <row r="727" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="727" spans="1:5">
       <c r="A727">
         <v>1210010</v>
       </c>
@@ -13582,7 +13546,7 @@
         <v>1389172</v>
       </c>
     </row>
-    <row r="728" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="728" spans="1:5">
       <c r="A728">
         <v>1210010</v>
       </c>
@@ -13599,7 +13563,7 @@
         <v>65862</v>
       </c>
     </row>
-    <row r="729" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="729" spans="1:5">
       <c r="A729">
         <v>1210010</v>
       </c>
@@ -13613,10 +13577,10 @@
         <v>189</v>
       </c>
       <c r="E729">
-        <v>141120</v>
-      </c>
-    </row>
-    <row r="730" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="730" spans="1:5">
       <c r="A730">
         <v>1210010</v>
       </c>
@@ -13633,7 +13597,7 @@
         <v>1812284</v>
       </c>
     </row>
-    <row r="731" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="731" spans="1:5">
       <c r="A731">
         <v>1210010</v>
       </c>
@@ -13650,7 +13614,7 @@
         <v>685646</v>
       </c>
     </row>
-    <row r="732" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="732" spans="1:5">
       <c r="A732">
         <v>1210010</v>
       </c>
@@ -13667,7 +13631,7 @@
         <v>108088</v>
       </c>
     </row>
-    <row r="733" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="733" spans="1:5">
       <c r="A733">
         <v>1210011</v>
       </c>
@@ -13684,7 +13648,7 @@
         <v>25099129</v>
       </c>
     </row>
-    <row r="734" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="734" spans="1:5">
       <c r="A734">
         <v>1210011</v>
       </c>
@@ -13698,10 +13662,10 @@
         <v>219</v>
       </c>
       <c r="E734">
-        <v>37277284</v>
-      </c>
-    </row>
-    <row r="735" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="735" spans="1:5">
       <c r="A735">
         <v>1210011</v>
       </c>
@@ -13718,7 +13682,7 @@
         <v>2518299</v>
       </c>
     </row>
-    <row r="736" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="736" spans="1:5">
       <c r="A736">
         <v>1210011</v>
       </c>
@@ -13735,7 +13699,7 @@
         <v>476400</v>
       </c>
     </row>
-    <row r="737" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="737" spans="1:5">
       <c r="A737">
         <v>1210011</v>
       </c>
@@ -13749,10 +13713,10 @@
         <v>189</v>
       </c>
       <c r="E737">
-        <v>434189</v>
-      </c>
-    </row>
-    <row r="738" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="738" spans="1:5">
       <c r="A738">
         <v>1210011</v>
       </c>
@@ -13769,7 +13733,7 @@
         <v>4331609</v>
       </c>
     </row>
-    <row r="739" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="739" spans="1:5">
       <c r="A739">
         <v>1210011</v>
       </c>
@@ -13786,7 +13750,7 @@
         <v>18153</v>
       </c>
     </row>
-    <row r="740" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="740" spans="1:5">
       <c r="A740">
         <v>1210011</v>
       </c>
@@ -13803,7 +13767,7 @@
         <v>208130</v>
       </c>
     </row>
-    <row r="741" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="741" spans="1:5">
       <c r="A741">
         <v>1210012</v>
       </c>
@@ -13820,7 +13784,7 @@
         <v>19008352</v>
       </c>
     </row>
-    <row r="742" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="742" spans="1:5">
       <c r="A742">
         <v>1210012</v>
       </c>
@@ -13837,7 +13801,7 @@
         <v>1503445</v>
       </c>
     </row>
-    <row r="743" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="743" spans="1:5">
       <c r="A743">
         <v>1210012</v>
       </c>
@@ -13854,7 +13818,7 @@
         <v>185025</v>
       </c>
     </row>
-    <row r="744" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="744" spans="1:5">
       <c r="A744">
         <v>1210012</v>
       </c>
@@ -13868,10 +13832,10 @@
         <v>189</v>
       </c>
       <c r="E744">
-        <v>72835</v>
-      </c>
-    </row>
-    <row r="745" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="745" spans="1:5">
       <c r="A745">
         <v>1210012</v>
       </c>
@@ -13888,7 +13852,7 @@
         <v>2005148</v>
       </c>
     </row>
-    <row r="746" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="746" spans="1:5">
       <c r="A746">
         <v>1210012</v>
       </c>
@@ -13905,7 +13869,7 @@
         <v>7965</v>
       </c>
     </row>
-    <row r="747" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="747" spans="1:5">
       <c r="A747">
         <v>1210012</v>
       </c>
@@ -13922,7 +13886,7 @@
         <v>97470</v>
       </c>
     </row>
-    <row r="748" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="748" spans="1:5">
       <c r="A748">
         <v>1210013</v>
       </c>
@@ -13939,7 +13903,7 @@
         <v>2244720</v>
       </c>
     </row>
-    <row r="749" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="749" spans="1:5">
       <c r="A749">
         <v>1210013</v>
       </c>
@@ -13953,10 +13917,10 @@
         <v>219</v>
       </c>
       <c r="E749">
-        <v>3097179</v>
-      </c>
-    </row>
-    <row r="750" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="750" spans="1:5">
       <c r="A750">
         <v>1210013</v>
       </c>
@@ -13973,7 +13937,7 @@
         <v>282309</v>
       </c>
     </row>
-    <row r="751" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="751" spans="1:5">
       <c r="A751">
         <v>1210013</v>
       </c>
@@ -13990,7 +13954,7 @@
         <v>12236</v>
       </c>
     </row>
-    <row r="752" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="752" spans="1:5">
       <c r="A752">
         <v>1210013</v>
       </c>
@@ -14007,7 +13971,7 @@
         <v>532245</v>
       </c>
     </row>
-    <row r="753" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="753" spans="1:5">
       <c r="A753">
         <v>1210013</v>
       </c>
@@ -14024,7 +13988,7 @@
         <v>30658</v>
       </c>
     </row>
-    <row r="754" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="754" spans="1:5">
       <c r="A754">
         <v>1210013</v>
       </c>
@@ -14041,7 +14005,7 @@
         <v>1641232</v>
       </c>
     </row>
-    <row r="755" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="755" spans="1:5">
       <c r="A755">
         <v>1210013</v>
       </c>
@@ -14058,7 +14022,7 @@
         <v>21773</v>
       </c>
     </row>
-    <row r="756" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="756" spans="1:5">
       <c r="A756">
         <v>1210014</v>
       </c>
@@ -14075,7 +14039,7 @@
         <v>20049597</v>
       </c>
     </row>
-    <row r="757" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="757" spans="1:5">
       <c r="A757">
         <v>1210014</v>
       </c>
@@ -14092,7 +14056,7 @@
         <v>1818829</v>
       </c>
     </row>
-    <row r="758" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="758" spans="1:5">
       <c r="A758">
         <v>1210014</v>
       </c>
@@ -14109,7 +14073,7 @@
         <v>139562524</v>
       </c>
     </row>
-    <row r="759" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="759" spans="1:5">
       <c r="A759">
         <v>1210014</v>
       </c>
@@ -14126,7 +14090,7 @@
         <v>93958</v>
       </c>
     </row>
-    <row r="760" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="760" spans="1:5">
       <c r="A760">
         <v>1210014</v>
       </c>
@@ -14143,7 +14107,7 @@
         <v>14959</v>
       </c>
     </row>
-    <row r="761" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="761" spans="1:5">
       <c r="A761">
         <v>1210014</v>
       </c>
@@ -14157,10 +14121,10 @@
         <v>189</v>
       </c>
       <c r="E761">
-        <v>615723</v>
-      </c>
-    </row>
-    <row r="762" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="762" spans="1:5">
       <c r="A762">
         <v>1210014</v>
       </c>
@@ -14177,7 +14141,7 @@
         <v>2259870</v>
       </c>
     </row>
-    <row r="763" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="763" spans="1:5">
       <c r="A763">
         <v>1210014</v>
       </c>
@@ -14194,7 +14158,7 @@
         <v>296812</v>
       </c>
     </row>
-    <row r="764" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="764" spans="1:5">
       <c r="A764">
         <v>1210014</v>
       </c>
@@ -14211,7 +14175,7 @@
         <v>15135519</v>
       </c>
     </row>
-    <row r="765" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="765" spans="1:5">
       <c r="A765">
         <v>1210014</v>
       </c>
@@ -14228,7 +14192,7 @@
         <v>1682323</v>
       </c>
     </row>
-    <row r="766" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="766" spans="1:5">
       <c r="A766">
         <v>1210014</v>
       </c>
@@ -14245,7 +14209,7 @@
         <v>357430655</v>
       </c>
     </row>
-    <row r="767" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="767" spans="1:5">
       <c r="A767">
         <v>1210014</v>
       </c>
@@ -14262,7 +14226,7 @@
         <v>14671280</v>
       </c>
     </row>
-    <row r="768" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="768" spans="1:5">
       <c r="A768">
         <v>1210014</v>
       </c>
@@ -14279,7 +14243,7 @@
         <v>-23138545</v>
       </c>
     </row>
-    <row r="769" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="769" spans="1:5">
       <c r="A769">
         <v>1210014</v>
       </c>
@@ -14296,7 +14260,7 @@
         <v>102459</v>
       </c>
     </row>
-    <row r="770" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="770" spans="1:5">
       <c r="A770">
         <v>1210014</v>
       </c>
@@ -14313,7 +14277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="771" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="771" spans="1:5">
       <c r="A771">
         <v>1210014</v>
       </c>
@@ -14330,7 +14294,7 @@
         <v>1850638</v>
       </c>
     </row>
-    <row r="772" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="772" spans="1:5">
       <c r="A772">
         <v>1210014</v>
       </c>
@@ -14347,7 +14311,7 @@
         <v>20843316</v>
       </c>
     </row>
-    <row r="773" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="773" spans="1:5">
       <c r="A773">
         <v>1210014</v>
       </c>
@@ -14364,7 +14328,7 @@
         <v>4330901</v>
       </c>
     </row>
-    <row r="774" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="774" spans="1:5">
       <c r="A774">
         <v>1210014</v>
       </c>
@@ -14381,7 +14345,7 @@
         <v>49360244</v>
       </c>
     </row>
-    <row r="775" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="775" spans="1:5">
       <c r="A775">
         <v>1210014</v>
       </c>
@@ -14398,7 +14362,7 @@
         <v>4438787</v>
       </c>
     </row>
-    <row r="776" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="776" spans="1:5">
       <c r="A776">
         <v>1210014</v>
       </c>
@@ -14415,7 +14379,7 @@
         <v>12976228</v>
       </c>
     </row>
-    <row r="777" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="777" spans="1:5">
       <c r="A777">
         <v>1210014</v>
       </c>
@@ -14432,7 +14396,7 @@
         <v>5580665</v>
       </c>
     </row>
-    <row r="778" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="778" spans="1:5">
       <c r="A778">
         <v>1210014</v>
       </c>
@@ -14449,7 +14413,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="779" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="779" spans="1:5">
       <c r="A779">
         <v>1210014</v>
       </c>
@@ -14466,7 +14430,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="780" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="780" spans="1:5">
       <c r="A780">
         <v>1210014</v>
       </c>
@@ -14483,7 +14447,7 @@
         <v>37412</v>
       </c>
     </row>
-    <row r="781" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="781" spans="1:5">
       <c r="A781">
         <v>1210014</v>
       </c>
@@ -14500,7 +14464,7 @@
         <v>14492</v>
       </c>
     </row>
-    <row r="782" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="782" spans="1:5">
       <c r="A782">
         <v>1210014</v>
       </c>
@@ -14517,7 +14481,7 @@
         <v>601778</v>
       </c>
     </row>
-    <row r="783" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="783" spans="1:5">
       <c r="A783">
         <v>1210014</v>
       </c>
@@ -14534,7 +14498,7 @@
         <v>18511323</v>
       </c>
     </row>
-    <row r="784" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="784" spans="1:5">
       <c r="A784">
         <v>1210014</v>
       </c>
@@ -14551,7 +14515,7 @@
         <v>10617143</v>
       </c>
     </row>
-    <row r="785" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="785" spans="1:5">
       <c r="A785">
         <v>1210014</v>
       </c>
@@ -14568,7 +14532,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="786" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="786" spans="1:5">
       <c r="A786">
         <v>1210015</v>
       </c>
@@ -14585,7 +14549,7 @@
         <v>372142584</v>
       </c>
     </row>
-    <row r="787" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="787" spans="1:5">
       <c r="A787">
         <v>1210015</v>
       </c>
@@ -14602,7 +14566,7 @@
         <v>23112582</v>
       </c>
     </row>
-    <row r="788" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="788" spans="1:5">
       <c r="A788">
         <v>1210015</v>
       </c>
@@ -14619,7 +14583,7 @@
         <v>-21721395</v>
       </c>
     </row>
-    <row r="789" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="789" spans="1:5">
       <c r="A789">
         <v>1210016</v>
       </c>
@@ -14636,7 +14600,7 @@
         <v>-81416</v>
       </c>
     </row>
-    <row r="790" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="790" spans="1:5">
       <c r="A790">
         <v>1210016</v>
       </c>
@@ -14653,7 +14617,7 @@
         <v>-76</v>
       </c>
     </row>
-    <row r="791" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="791" spans="1:5">
       <c r="A791">
         <v>1210016</v>
       </c>
@@ -14670,7 +14634,7 @@
         <v>-1826</v>
       </c>
     </row>
-    <row r="792" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="792" spans="1:5">
       <c r="A792">
         <v>1210017</v>
       </c>
@@ -14687,7 +14651,7 @@
         <v>4211643</v>
       </c>
     </row>
-    <row r="793" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="793" spans="1:5">
       <c r="A793">
         <v>1210017</v>
       </c>
@@ -14704,7 +14668,7 @@
         <v>369448</v>
       </c>
     </row>
-    <row r="794" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="794" spans="1:5">
       <c r="A794">
         <v>1210017</v>
       </c>
@@ -14721,7 +14685,7 @@
         <v>284301</v>
       </c>
     </row>
-    <row r="795" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="795" spans="1:5">
       <c r="A795">
         <v>1210017</v>
       </c>
@@ -14738,7 +14702,7 @@
         <v>20716</v>
       </c>
     </row>
-    <row r="796" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="796" spans="1:5">
       <c r="A796">
         <v>1210018</v>
       </c>
@@ -14755,7 +14719,7 @@
         <v>304759</v>
       </c>
     </row>
-    <row r="797" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="797" spans="1:5">
       <c r="A797">
         <v>1210018</v>
       </c>
@@ -14772,7 +14736,7 @@
         <v>2634154</v>
       </c>
     </row>
-    <row r="798" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="798" spans="1:5">
       <c r="A798">
         <v>1210019</v>
       </c>
@@ -14789,7 +14753,7 @@
         <v>7509946</v>
       </c>
     </row>
-    <row r="799" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="799" spans="1:5">
       <c r="A799">
         <v>1210019</v>
       </c>
@@ -14806,7 +14770,7 @@
         <v>345846</v>
       </c>
     </row>
-    <row r="800" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="800" spans="1:5">
       <c r="A800">
         <v>1210019</v>
       </c>
@@ -14823,7 +14787,7 @@
         <v>845596</v>
       </c>
     </row>
-    <row r="801" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="801" spans="1:5">
       <c r="A801">
         <v>1210019</v>
       </c>
@@ -14840,7 +14804,7 @@
         <v>17754</v>
       </c>
     </row>
-    <row r="802" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="802" spans="1:5">
       <c r="A802">
         <v>1210019</v>
       </c>
@@ -14857,7 +14821,7 @@
         <v>26340</v>
       </c>
     </row>
-    <row r="803" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="803" spans="1:5">
       <c r="A803">
         <v>1210019</v>
       </c>
@@ -14874,7 +14838,7 @@
         <v>35705</v>
       </c>
     </row>
-    <row r="804" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="804" spans="1:5">
       <c r="A804">
         <v>1210019</v>
       </c>
@@ -14891,7 +14855,7 @@
         <v>11339</v>
       </c>
     </row>
-    <row r="805" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="805" spans="1:5">
       <c r="A805">
         <v>1210019</v>
       </c>
@@ -14908,7 +14872,7 @@
         <v>723501</v>
       </c>
     </row>
-    <row r="806" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="806" spans="1:5">
       <c r="A806">
         <v>1210019</v>
       </c>
@@ -14925,7 +14889,7 @@
         <v>28998</v>
       </c>
     </row>
-    <row r="807" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="807" spans="1:5">
       <c r="A807">
         <v>1210019</v>
       </c>
@@ -14942,7 +14906,7 @@
         <v>38481</v>
       </c>
     </row>
-    <row r="808" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="808" spans="1:5">
       <c r="A808">
         <v>1210019</v>
       </c>
@@ -14959,7 +14923,7 @@
         <v>1306309</v>
       </c>
     </row>
-    <row r="809" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="809" spans="1:5">
       <c r="A809">
         <v>1210019</v>
       </c>
@@ -14976,7 +14940,7 @@
         <v>739653</v>
       </c>
     </row>
-    <row r="810" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="810" spans="1:5">
       <c r="A810">
         <v>1220001</v>
       </c>
@@ -14993,7 +14957,7 @@
         <v>95744208</v>
       </c>
     </row>
-    <row r="811" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="811" spans="1:5">
       <c r="A811">
         <v>1220001</v>
       </c>
@@ -15010,7 +14974,7 @@
         <v>13043986</v>
       </c>
     </row>
-    <row r="812" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="812" spans="1:5">
       <c r="A812">
         <v>1220001</v>
       </c>
@@ -15027,7 +14991,7 @@
         <v>-1909690</v>
       </c>
     </row>
-    <row r="813" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="813" spans="1:5">
       <c r="A813">
         <v>1220002</v>
       </c>
@@ -15044,7 +15008,7 @@
         <v>1983639</v>
       </c>
     </row>
-    <row r="814" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="814" spans="1:5">
       <c r="A814">
         <v>1220002</v>
       </c>
@@ -15061,7 +15025,7 @@
         <v>158992</v>
       </c>
     </row>
-    <row r="815" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="815" spans="1:5">
       <c r="A815">
         <v>1230001</v>
       </c>
@@ -15078,7 +15042,7 @@
         <v>46032314</v>
       </c>
     </row>
-    <row r="816" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="816" spans="1:5">
       <c r="A816">
         <v>1230001</v>
       </c>
@@ -15092,10 +15056,10 @@
         <v>219</v>
       </c>
       <c r="E816">
-        <v>1781353</v>
-      </c>
-    </row>
-    <row r="817" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="817" spans="1:5">
       <c r="A817">
         <v>1230001</v>
       </c>
@@ -15112,7 +15076,7 @@
         <v>7860569</v>
       </c>
     </row>
-    <row r="818" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="818" spans="1:5">
       <c r="A818">
         <v>1230001</v>
       </c>
@@ -15129,7 +15093,7 @@
         <v>1551680</v>
       </c>
     </row>
-    <row r="819" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="819" spans="1:5">
       <c r="A819">
         <v>1230001</v>
       </c>
@@ -15146,7 +15110,7 @@
         <v>3416174</v>
       </c>
     </row>
-    <row r="820" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="820" spans="1:5">
       <c r="A820">
         <v>1230001</v>
       </c>
@@ -15163,7 +15127,7 @@
         <v>177370</v>
       </c>
     </row>
-    <row r="821" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="821" spans="1:5">
       <c r="A821">
         <v>1230002</v>
       </c>
@@ -15180,7 +15144,7 @@
         <v>217489443</v>
       </c>
     </row>
-    <row r="822" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="822" spans="1:5">
       <c r="A822">
         <v>1230002</v>
       </c>
@@ -15197,7 +15161,7 @@
         <v>19913250</v>
       </c>
     </row>
-    <row r="823" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="823" spans="1:5">
       <c r="A823">
         <v>1230002</v>
       </c>
@@ -15214,7 +15178,7 @@
         <v>4116590</v>
       </c>
     </row>
-    <row r="824" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="824" spans="1:5">
       <c r="A824">
         <v>1230003</v>
       </c>
@@ -15231,7 +15195,7 @@
         <v>2944068</v>
       </c>
     </row>
-    <row r="825" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="825" spans="1:5">
       <c r="A825">
         <v>1230003</v>
       </c>
@@ -15248,7 +15212,7 @@
         <v>233104</v>
       </c>
     </row>
-    <row r="826" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="826" spans="1:5">
       <c r="A826">
         <v>1230003</v>
       </c>
@@ -15265,7 +15229,7 @@
         <v>320020</v>
       </c>
     </row>
-    <row r="827" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="827" spans="1:5">
       <c r="A827">
         <v>1230003</v>
       </c>
@@ -15282,7 +15246,7 @@
         <v>32372545</v>
       </c>
     </row>
-    <row r="828" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="828" spans="1:5">
       <c r="A828">
         <v>1230003</v>
       </c>
@@ -15299,7 +15263,7 @@
         <v>16747456</v>
       </c>
     </row>
-    <row r="829" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="829" spans="1:5">
       <c r="A829">
         <v>1230003</v>
       </c>
@@ -15316,7 +15280,7 @@
         <v>396397287</v>
       </c>
     </row>
-    <row r="830" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="830" spans="1:5">
       <c r="A830">
         <v>1230003</v>
       </c>
@@ -15333,7 +15297,7 @@
         <v>5888655</v>
       </c>
     </row>
-    <row r="831" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="831" spans="1:5">
       <c r="A831">
         <v>1230003</v>
       </c>
@@ -15350,7 +15314,7 @@
         <v>44083012</v>
       </c>
     </row>
-    <row r="832" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="832" spans="1:5">
       <c r="A832">
         <v>1230003</v>
       </c>
@@ -15367,7 +15331,7 @@
         <v>515396</v>
       </c>
     </row>
-    <row r="833" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="833" spans="1:5">
       <c r="A833">
         <v>1230003</v>
       </c>
@@ -15384,7 +15348,7 @@
         <v>-1540085</v>
       </c>
     </row>
-    <row r="834" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="834" spans="1:5">
       <c r="A834">
         <v>1230003</v>
       </c>
@@ -15401,7 +15365,7 @@
         <v>-9680686</v>
       </c>
     </row>
-    <row r="835" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="835" spans="1:5">
       <c r="A835">
         <v>1230003</v>
       </c>
@@ -15418,7 +15382,7 @@
         <v>14835</v>
       </c>
     </row>
-    <row r="836" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="836" spans="1:5">
       <c r="A836">
         <v>1230004</v>
       </c>
@@ -15435,7 +15399,7 @@
         <v>6794138</v>
       </c>
     </row>
-    <row r="837" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="837" spans="1:5">
       <c r="A837">
         <v>1230004</v>
       </c>
@@ -15449,10 +15413,10 @@
         <v>219</v>
       </c>
       <c r="E837">
-        <v>9514287</v>
-      </c>
-    </row>
-    <row r="838" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="838" spans="1:5">
       <c r="A838">
         <v>1230004</v>
       </c>
@@ -15469,7 +15433,7 @@
         <v>1102429</v>
       </c>
     </row>
-    <row r="839" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="839" spans="1:5">
       <c r="A839">
         <v>1230004</v>
       </c>
@@ -15486,7 +15450,7 @@
         <v>112977</v>
       </c>
     </row>
-    <row r="840" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="840" spans="1:5">
       <c r="A840">
         <v>1230004</v>
       </c>
@@ -15500,10 +15464,10 @@
         <v>189</v>
       </c>
       <c r="E840">
-        <v>80296</v>
-      </c>
-    </row>
-    <row r="841" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="841" spans="1:5">
       <c r="A841">
         <v>1230004</v>
       </c>
@@ -15520,7 +15484,7 @@
         <v>952183</v>
       </c>
     </row>
-    <row r="842" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="842" spans="1:5">
       <c r="A842">
         <v>1230004</v>
       </c>
@@ -15537,7 +15501,7 @@
         <v>24944</v>
       </c>
     </row>
-    <row r="843" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="843" spans="1:5">
       <c r="A843">
         <v>1230005</v>
       </c>
@@ -15554,7 +15518,7 @@
         <v>40959154</v>
       </c>
     </row>
-    <row r="844" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="844" spans="1:5">
       <c r="A844">
         <v>1230005</v>
       </c>
@@ -15568,10 +15532,10 @@
         <v>219</v>
       </c>
       <c r="E844">
-        <v>2692824</v>
-      </c>
-    </row>
-    <row r="845" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="845" spans="1:5">
       <c r="A845">
         <v>1230005</v>
       </c>
@@ -15588,7 +15552,7 @@
         <v>2231250</v>
       </c>
     </row>
-    <row r="846" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="846" spans="1:5">
       <c r="A846">
         <v>1230005</v>
       </c>
@@ -15605,7 +15569,7 @@
         <v>244426</v>
       </c>
     </row>
-    <row r="847" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="847" spans="1:5">
       <c r="A847">
         <v>1230005</v>
       </c>
@@ -15619,10 +15583,10 @@
         <v>189</v>
       </c>
       <c r="E847">
-        <v>1133115</v>
-      </c>
-    </row>
-    <row r="848" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="848" spans="1:5">
       <c r="A848">
         <v>1230005</v>
       </c>
@@ -15639,7 +15603,7 @@
         <v>2799665</v>
       </c>
     </row>
-    <row r="849" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="849" spans="1:5">
       <c r="A849">
         <v>1230005</v>
       </c>
@@ -15656,7 +15620,7 @@
         <v>171615</v>
       </c>
     </row>
-    <row r="850" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="850" spans="1:5">
       <c r="A850">
         <v>1230006</v>
       </c>
@@ -15673,7 +15637,7 @@
         <v>26425973</v>
       </c>
     </row>
-    <row r="851" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="851" spans="1:5">
       <c r="A851">
         <v>1230006</v>
       </c>
@@ -15687,10 +15651,10 @@
         <v>219</v>
       </c>
       <c r="E851">
-        <v>5101889</v>
-      </c>
-    </row>
-    <row r="852" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="852" spans="1:5">
       <c r="A852">
         <v>1230006</v>
       </c>
@@ -15707,7 +15671,7 @@
         <v>1648926</v>
       </c>
     </row>
-    <row r="853" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="853" spans="1:5">
       <c r="A853">
         <v>1230006</v>
       </c>
@@ -15724,7 +15688,7 @@
         <v>190065</v>
       </c>
     </row>
-    <row r="854" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="854" spans="1:5">
       <c r="A854">
         <v>1230006</v>
       </c>
@@ -15741,7 +15705,7 @@
         <v>1822890</v>
       </c>
     </row>
-    <row r="855" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="855" spans="1:5">
       <c r="A855">
         <v>1230006</v>
       </c>
@@ -15758,7 +15722,7 @@
         <v>87007</v>
       </c>
     </row>
-    <row r="856" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="856" spans="1:5">
       <c r="A856">
         <v>1230007</v>
       </c>
@@ -15775,7 +15739,7 @@
         <v>5505386</v>
       </c>
     </row>
-    <row r="857" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="857" spans="1:5">
       <c r="A857">
         <v>1230007</v>
       </c>
@@ -15792,7 +15756,7 @@
         <v>5162785</v>
       </c>
     </row>
-    <row r="858" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="858" spans="1:5">
       <c r="A858">
         <v>1230008</v>
       </c>
@@ -15809,7 +15773,7 @@
         <v>33430992</v>
       </c>
     </row>
-    <row r="859" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="859" spans="1:5">
       <c r="A859">
         <v>1230008</v>
       </c>
@@ -15826,7 +15790,7 @@
         <v>18518441</v>
       </c>
     </row>
-    <row r="860" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="860" spans="1:5">
       <c r="A860">
         <v>1230009</v>
       </c>
@@ -15843,7 +15807,7 @@
         <v>12445196</v>
       </c>
     </row>
-    <row r="861" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="861" spans="1:5">
       <c r="A861">
         <v>1230009</v>
       </c>
@@ -15860,7 +15824,7 @@
         <v>919699</v>
       </c>
     </row>
-    <row r="862" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="862" spans="1:5">
       <c r="A862">
         <v>1230009</v>
       </c>
@@ -15877,7 +15841,7 @@
         <v>1283548</v>
       </c>
     </row>
-    <row r="863" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="863" spans="1:5">
       <c r="A863">
         <v>1230009</v>
       </c>
@@ -15894,7 +15858,7 @@
         <v>52856</v>
       </c>
     </row>
-    <row r="864" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="864" spans="1:5">
       <c r="A864">
         <v>1230010</v>
       </c>
@@ -15911,7 +15875,7 @@
         <v>5274680</v>
       </c>
     </row>
-    <row r="865" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="865" spans="1:5">
       <c r="A865">
         <v>1230010</v>
       </c>
@@ -15928,7 +15892,7 @@
         <v>444917</v>
       </c>
     </row>
-    <row r="866" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="866" spans="1:5">
       <c r="A866">
         <v>1230010</v>
       </c>
@@ -15945,7 +15909,7 @@
         <v>283371</v>
       </c>
     </row>
-    <row r="867" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="867" spans="1:5">
       <c r="A867">
         <v>1230010</v>
       </c>
@@ -15962,7 +15926,7 @@
         <v>33413</v>
       </c>
     </row>
-    <row r="868" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="868" spans="1:5">
       <c r="A868">
         <v>1230011</v>
       </c>
@@ -15979,7 +15943,7 @@
         <v>62672234</v>
       </c>
     </row>
-    <row r="869" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="869" spans="1:5">
       <c r="A869">
         <v>1230011</v>
       </c>
@@ -15993,10 +15957,10 @@
         <v>219</v>
       </c>
       <c r="E869">
-        <v>11826423</v>
-      </c>
-    </row>
-    <row r="870" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="870" spans="1:5">
       <c r="A870">
         <v>1230011</v>
       </c>
@@ -16013,7 +15977,7 @@
         <v>810220</v>
       </c>
     </row>
-    <row r="871" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="871" spans="1:5">
       <c r="A871">
         <v>1230011</v>
       </c>
@@ -16027,10 +15991,10 @@
         <v>189</v>
       </c>
       <c r="E871">
-        <v>137342</v>
-      </c>
-    </row>
-    <row r="872" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="872" spans="1:5">
       <c r="A872">
         <v>1230011</v>
       </c>
@@ -16047,7 +16011,7 @@
         <v>5015899</v>
       </c>
     </row>
-    <row r="873" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="873" spans="1:5">
       <c r="A873">
         <v>1230011</v>
       </c>
@@ -16064,7 +16028,7 @@
         <v>251659</v>
       </c>
     </row>
-    <row r="874" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="874" spans="1:5">
       <c r="A874">
         <v>1230012</v>
       </c>
@@ -16081,7 +16045,7 @@
         <v>403570</v>
       </c>
     </row>
-    <row r="875" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="875" spans="1:5">
       <c r="A875">
         <v>1230013</v>
       </c>
@@ -16098,7 +16062,7 @@
         <v>93198018</v>
       </c>
     </row>
-    <row r="876" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="876" spans="1:5">
       <c r="A876">
         <v>1230013</v>
       </c>
@@ -16115,7 +16079,7 @@
         <v>78329</v>
       </c>
     </row>
-    <row r="877" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="877" spans="1:5">
       <c r="A877">
         <v>1230014</v>
       </c>
@@ -16132,7 +16096,7 @@
         <v>5946020</v>
       </c>
     </row>
-    <row r="878" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="878" spans="1:5">
       <c r="A878">
         <v>1230014</v>
       </c>
@@ -16149,7 +16113,7 @@
         <v>499543</v>
       </c>
     </row>
-    <row r="879" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="879" spans="1:5">
       <c r="A879">
         <v>1230014</v>
       </c>
@@ -16166,7 +16130,7 @@
         <v>620981</v>
       </c>
     </row>
-    <row r="880" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="880" spans="1:5">
       <c r="A880">
         <v>1230014</v>
       </c>
@@ -16183,7 +16147,7 @@
         <v>29316</v>
       </c>
     </row>
-    <row r="881" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="881" spans="1:5">
       <c r="A881">
         <v>1230015</v>
       </c>
@@ -16200,7 +16164,7 @@
         <v>1237164</v>
       </c>
     </row>
-    <row r="882" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="882" spans="1:5">
       <c r="A882">
         <v>1230015</v>
       </c>
@@ -16214,10 +16178,10 @@
         <v>219</v>
       </c>
       <c r="E882">
-        <v>423840</v>
-      </c>
-    </row>
-    <row r="883" spans="1:5" x14ac:dyDescent="0.45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="883" spans="1:5">
       <c r="A883">
         <v>1230015</v>
       </c>
@@ -16234,7 +16198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="884" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="884" spans="1:5">
       <c r="A884">
         <v>1240001</v>
       </c>
@@ -16251,7 +16215,7 @@
         <v>32781889</v>
       </c>
     </row>
-    <row r="885" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="885" spans="1:5">
       <c r="A885">
         <v>1240001</v>
       </c>
@@ -16268,7 +16232,7 @@
         <v>956110</v>
       </c>
     </row>
-    <row r="886" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="886" spans="1:5">
       <c r="A886">
         <v>1240001</v>
       </c>
@@ -16285,7 +16249,7 @@
         <v>-2733124</v>
       </c>
     </row>
-    <row r="887" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="887" spans="1:5">
       <c r="A887">
         <v>1240002</v>
       </c>
@@ -16302,7 +16266,7 @@
         <v>-863178290</v>
       </c>
     </row>
-    <row r="888" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="888" spans="1:5">
       <c r="A888">
         <v>1240002</v>
       </c>
@@ -16319,7 +16283,7 @@
         <v>2076229</v>
       </c>
     </row>
-    <row r="889" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="889" spans="1:5">
       <c r="A889">
         <v>1240002</v>
       </c>
@@ -16336,7 +16300,7 @@
         <v>-1573447</v>
       </c>
     </row>
-    <row r="890" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="890" spans="1:5">
       <c r="A890">
         <v>1240002</v>
       </c>
@@ -16353,7 +16317,7 @@
         <v>-392753348</v>
       </c>
     </row>
-    <row r="891" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="891" spans="1:5">
       <c r="A891">
         <v>1240002</v>
       </c>
@@ -16370,7 +16334,7 @@
         <v>-1456160</v>
       </c>
     </row>
-    <row r="892" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="892" spans="1:5">
       <c r="A892">
         <v>1240002</v>
       </c>
@@ -16387,7 +16351,7 @@
         <v>-3726430</v>
       </c>
     </row>
-    <row r="893" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="893" spans="1:5">
       <c r="A893">
         <v>1240002</v>
       </c>
@@ -16404,7 +16368,7 @@
         <v>162639645</v>
       </c>
     </row>
-    <row r="894" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="894" spans="1:5">
       <c r="A894">
         <v>1240002</v>
       </c>
@@ -16421,7 +16385,7 @@
         <v>869508708</v>
       </c>
     </row>
-    <row r="895" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="895" spans="1:5">
       <c r="A895">
         <v>1240002</v>
       </c>
@@ -16438,7 +16402,7 @@
         <v>20741909</v>
       </c>
     </row>
-    <row r="896" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="896" spans="1:5">
       <c r="A896">
         <v>1240002</v>
       </c>
@@ -16455,7 +16419,7 @@
         <v>117193301</v>
       </c>
     </row>
-    <row r="897" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="897" spans="1:5">
       <c r="A897">
         <v>1240002</v>
       </c>
@@ -16472,7 +16436,7 @@
         <v>84412652</v>
       </c>
     </row>
-    <row r="898" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="898" spans="1:5">
       <c r="A898">
         <v>1240002</v>
       </c>
@@ -16489,7 +16453,7 @@
         <v>2436310170</v>
       </c>
     </row>
-    <row r="899" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="899" spans="1:5">
       <c r="A899">
         <v>1240002</v>
       </c>
@@ -16506,7 +16470,7 @@
         <v>1514728</v>
       </c>
     </row>
-    <row r="900" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="900" spans="1:5">
       <c r="A900">
         <v>1240002</v>
       </c>
@@ -16523,7 +16487,7 @@
         <v>2969115</v>
       </c>
     </row>
-    <row r="901" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="901" spans="1:5">
       <c r="A901">
         <v>1240002</v>
       </c>
@@ -16540,7 +16504,7 @@
         <v>1957861</v>
       </c>
     </row>
-    <row r="902" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="902" spans="1:5">
       <c r="A902">
         <v>1240002</v>
       </c>
@@ -16557,7 +16521,7 @@
         <v>157986</v>
       </c>
     </row>
-    <row r="903" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="903" spans="1:5">
       <c r="A903">
         <v>1240002</v>
       </c>
@@ -16574,7 +16538,7 @@
         <v>22925737</v>
       </c>
     </row>
-    <row r="904" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="904" spans="1:5">
       <c r="A904">
         <v>1240002</v>
       </c>
@@ -16591,7 +16555,7 @@
         <v>10303996</v>
       </c>
     </row>
-    <row r="905" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="905" spans="1:5">
       <c r="A905">
         <v>1240002</v>
       </c>
@@ -16608,7 +16572,7 @@
         <v>102618138</v>
       </c>
     </row>
-    <row r="906" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="906" spans="1:5">
       <c r="A906">
         <v>1240002</v>
       </c>
@@ -16625,7 +16589,7 @@
         <v>125031942</v>
       </c>
     </row>
-    <row r="907" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="907" spans="1:5">
       <c r="A907">
         <v>1240002</v>
       </c>
@@ -16642,7 +16606,7 @@
         <v>1352098</v>
       </c>
     </row>
-    <row r="908" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="908" spans="1:5">
       <c r="A908">
         <v>1240002</v>
       </c>
@@ -16659,7 +16623,7 @@
         <v>989254</v>
       </c>
     </row>
-    <row r="909" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="909" spans="1:5">
       <c r="A909">
         <v>1240002</v>
       </c>
@@ -16676,7 +16640,7 @@
         <v>3429</v>
       </c>
     </row>
-    <row r="910" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="910" spans="1:5">
       <c r="A910">
         <v>1240002</v>
       </c>
@@ -16693,7 +16657,7 @@
         <v>63129692</v>
       </c>
     </row>
-    <row r="911" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="911" spans="1:5">
       <c r="A911">
         <v>1240002</v>
       </c>
@@ -16710,7 +16674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="912" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="912" spans="1:5">
       <c r="A912">
         <v>1240002</v>
       </c>
@@ -16727,7 +16691,7 @@
         <v>-90020215</v>
       </c>
     </row>
-    <row r="913" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="913" spans="1:5">
       <c r="A913">
         <v>1240002</v>
       </c>
@@ -16744,7 +16708,7 @@
         <v>13306240</v>
       </c>
     </row>
-    <row r="914" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="914" spans="1:5">
       <c r="A914">
         <v>1240002</v>
       </c>
@@ -16761,7 +16725,7 @@
         <v>151942</v>
       </c>
     </row>
-    <row r="915" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="915" spans="1:5">
       <c r="A915">
         <v>1240002</v>
       </c>
@@ -16778,7 +16742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="916" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="916" spans="1:5">
       <c r="A916">
         <v>1240002</v>
       </c>
@@ -16795,7 +16759,7 @@
         <v>1627205</v>
       </c>
     </row>
-    <row r="917" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="917" spans="1:5">
       <c r="A917">
         <v>1240002</v>
       </c>
@@ -16812,16 +16776,7 @@
         <v>17635644</v>
       </c>
     </row>
-    <row r="918" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="D918" t="s">
-        <v>271</v>
-      </c>
-      <c r="E918">
-        <v>12800057779</v>
-      </c>
-    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>